--- a/cosco-shipping/数据源/中远海控_行业供需与运价数据.xlsx
+++ b/cosco-shipping/数据源/中远海控_行业供需与运价数据.xlsx
@@ -516,7 +516,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L31"/>
+  <dimension ref="A1:L32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -1912,6 +1912,50 @@
       <c r="L31" t="inlineStr">
         <is>
           <t>SCFI报3355.24(+2.4%)，CCFI报1846.96(+0.4%)。欧洲2945(-0.6%)、地中海3929(-2.9%)回落；美西6714(+3.5%)、美东9568(+3.0%)上涨；波斯湾5422(+3.1%)因中东紧张续涨。</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>3409.63</v>
+      </c>
+      <c r="C32" t="n">
+        <v>0.016</v>
+      </c>
+      <c r="D32" t="n">
+        <v>1821.65</v>
+      </c>
+      <c r="E32" t="n">
+        <v>-0.014</v>
+      </c>
+      <c r="F32" t="n">
+        <v>2842</v>
+      </c>
+      <c r="G32" t="n">
+        <v>3767</v>
+      </c>
+      <c r="H32" t="n">
+        <v>6765</v>
+      </c>
+      <c r="I32" t="n">
+        <v>9700</v>
+      </c>
+      <c r="J32" t="n">
+        <v>5729</v>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>&gt;95%</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>SCFI报3409.63(+1.6%)，CCFI报1821.65(-1.4%)。欧洲2842(-3.5%)、地中海3767(-4.1%)回落；美西6765(+0.8%)、美东9700(+1.4%)上涨；波斯湾5729(+5.7%)因中东紧张续涨。</t>
         </is>
       </c>
     </row>

--- a/cosco-shipping/数据源/中远海控_行业供需与运价数据.xlsx
+++ b/cosco-shipping/数据源/中远海控_行业供需与运价数据.xlsx
@@ -516,7 +516,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L32"/>
+  <dimension ref="A1:L33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -1956,6 +1956,50 @@
       <c r="L32" t="inlineStr">
         <is>
           <t>SCFI报3409.63(+1.6%)，CCFI报1821.65(-1.4%)。欧洲2842(-3.5%)、地中海3767(-4.1%)回落；美西6765(+0.8%)、美东9700(+1.4%)上涨；波斯湾5729(+5.7%)因中东紧张续涨。</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>3509.53</v>
+      </c>
+      <c r="C33" t="n">
+        <v>0.029</v>
+      </c>
+      <c r="D33" t="n">
+        <v>1833.99</v>
+      </c>
+      <c r="E33" t="n">
+        <v>0.007</v>
+      </c>
+      <c r="F33" t="n">
+        <v>2716</v>
+      </c>
+      <c r="G33" t="n">
+        <v>3557</v>
+      </c>
+      <c r="H33" t="n">
+        <v>6940</v>
+      </c>
+      <c r="I33" t="n">
+        <v>10046</v>
+      </c>
+      <c r="J33" t="n">
+        <v>6139</v>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>&gt;95%</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>SCFI报3509.53(+2.9%)，CCFI报1833.99(+0.7%)。欧洲2716(-4.4%)、地中海3557(-5.6%)继续回落；美西6940(+2.6%)、美东10046(+3.6%)受巴拿马运河水位下降、舱位紧张带动续涨；波斯湾6139(+7.1%)大幅反弹；澳新2471(+6.7%)、南美8663(+11.0%)同步上涨。</t>
         </is>
       </c>
     </row>

--- a/cosco-shipping/数据源/中远海控_行业供需与运价数据.xlsx
+++ b/cosco-shipping/数据源/中远海控_行业供需与运价数据.xlsx
@@ -23,7 +23,7 @@
     <numFmt numFmtId="164" formatCode="+0.0%;-0.0%;0.0%"/>
     <numFmt numFmtId="165" formatCode="$#,##0"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="6">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -32,20 +32,38 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b val="1"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <color rgb="FF175CEB"/>
+      <sz val="10"/>
+      <u val="single"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Segoe UI Symbol"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
+      <sz val="10"/>
     </font>
     <font>
       <name val="Microsoft YaHei"/>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
+      <color rgb="FFFFFFFF"/>
       <sz val="11"/>
     </font>
     <font>
       <name val="Microsoft YaHei"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -54,18 +72,21 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="001F497D"/>
-        <bgColor rgb="001F497D"/>
+        <fgColor rgb="FF1F497D"/>
+        <bgColor rgb="FF1F497D"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F2F5F9"/>
-        <bgColor rgb="00F2F5F9"/>
+        <fgColor rgb="FFF2F5F9"/>
+        <bgColor rgb="FFF2F5F9"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill/>
+    </fill>
   </fills>
-  <borders count="3">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -81,81 +102,136 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="00D9D9D9"/>
+        <color rgb="FFD9D9D9"/>
       </left>
       <right style="thin">
-        <color rgb="00D9D9D9"/>
+        <color rgb="FFD9D9D9"/>
       </right>
       <top style="thin">
-        <color rgb="00D9D9D9"/>
+        <color rgb="FFD9D9D9"/>
       </top>
       <bottom style="thin">
-        <color rgb="00D9D9D9"/>
+        <color rgb="FFD9D9D9"/>
       </bottom>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="3"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="40">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="4" fontId="3" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="4" fontId="4" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="4" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="3" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="4" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="4" fontId="3" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="4" fontId="4" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="4" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="3" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="4" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="3" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="5" fillId="4" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="5" fillId="4" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="5" fillId="4" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="4" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="3" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="3" fontId="4" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="4" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="5" fillId="4" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="00000000"/>
@@ -516,1490 +592,1534 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L33"/>
+  <dimension ref="A1:L34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="13" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="20" customWidth="1" min="6" max="6"/>
-    <col width="22" customWidth="1" min="7" max="7"/>
-    <col width="20" customWidth="1" min="8" max="8"/>
-    <col width="20" customWidth="1" min="9" max="9"/>
-    <col width="22" customWidth="1" min="10" max="10"/>
-    <col width="13" customWidth="1" min="11" max="11"/>
-    <col width="79" customWidth="1" min="12" max="12"/>
+    <col width="13" customWidth="1" style="25" min="1" max="1"/>
+    <col width="15" customWidth="1" style="25" min="2" max="2"/>
+    <col width="16" customWidth="1" style="25" min="3" max="3"/>
+    <col width="15" customWidth="1" style="25" min="4" max="4"/>
+    <col width="16" customWidth="1" style="25" min="5" max="5"/>
+    <col width="20" customWidth="1" style="25" min="6" max="6"/>
+    <col width="22" customWidth="1" style="25" min="7" max="7"/>
+    <col width="20" customWidth="1" style="25" min="8" max="8"/>
+    <col width="20" customWidth="1" style="25" min="9" max="9"/>
+    <col width="22" customWidth="1" style="25" min="10" max="10"/>
+    <col width="13" customWidth="1" style="25" min="11" max="11"/>
+    <col width="79" customWidth="1" style="25" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="26" t="inlineStr">
         <is>
           <t>日期</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="26" t="inlineStr">
         <is>
           <t>SCFI综合指数</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="26" t="inlineStr">
         <is>
           <t>SCFI周环比(%)</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="D1" s="26" t="inlineStr">
         <is>
           <t>CCFI综合指数</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="E1" s="26" t="inlineStr">
         <is>
           <t>CCFI周环比(%)</t>
         </is>
       </c>
-      <c r="F1" s="2" t="inlineStr">
+      <c r="F1" s="26" t="inlineStr">
         <is>
           <t>欧洲航线(USD/TEU)</t>
         </is>
       </c>
-      <c r="G1" s="2" t="inlineStr">
+      <c r="G1" s="26" t="inlineStr">
         <is>
           <t>地中海航线(USD/TEU)</t>
         </is>
       </c>
-      <c r="H1" s="2" t="inlineStr">
+      <c r="H1" s="26" t="inlineStr">
         <is>
           <t>美西航线(USD/FEU)</t>
         </is>
       </c>
-      <c r="I1" s="2" t="inlineStr">
+      <c r="I1" s="26" t="inlineStr">
         <is>
           <t>美东航线(USD/FEU)</t>
         </is>
       </c>
-      <c r="J1" s="2" t="inlineStr">
+      <c r="J1" s="26" t="inlineStr">
         <is>
           <t>波斯湾航线(USD/TEU)</t>
         </is>
       </c>
-      <c r="K1" s="2" t="inlineStr">
+      <c r="K1" s="26" t="inlineStr">
         <is>
           <t>舱位利用率</t>
         </is>
       </c>
-      <c r="L1" s="2" t="inlineStr">
+      <c r="L1" s="26" t="inlineStr">
         <is>
           <t>市场行情简评</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="inlineStr">
+      <c r="A2" s="27" t="inlineStr">
         <is>
           <t>2026-01-09</t>
         </is>
       </c>
-      <c r="B2" s="4" t="n">
+      <c r="B2" s="6" t="n">
         <v>1647.39</v>
       </c>
-      <c r="C2" s="5" t="n">
+      <c r="C2" s="28" t="n">
         <v>0</v>
       </c>
-      <c r="D2" s="4" t="n">
+      <c r="D2" s="6" t="n">
         <v>1197.6</v>
       </c>
-      <c r="E2" s="5" t="n">
+      <c r="E2" s="28" t="n">
         <v>0.024</v>
       </c>
-      <c r="F2" s="6" t="n">
+      <c r="F2" s="29" t="n">
         <v>1719</v>
       </c>
-      <c r="G2" s="6" t="n">
+      <c r="G2" s="29" t="n">
         <v>3232</v>
       </c>
-      <c r="H2" s="6" t="n">
+      <c r="H2" s="29" t="n">
         <v>2218</v>
       </c>
-      <c r="I2" s="6" t="n">
+      <c r="I2" s="29" t="n">
         <v>3128</v>
       </c>
-      <c r="J2" s="6" t="n">
+      <c r="J2" s="29" t="n">
         <v>1981</v>
       </c>
-      <c r="K2" s="7" t="inlineStr">
+      <c r="K2" s="30" t="inlineStr">
         <is>
           <t>95%</t>
         </is>
       </c>
-      <c r="L2" s="8" t="inlineStr">
+      <c r="L2" s="31" t="inlineStr">
         <is>
           <t>SCFI报1647.39。欧洲1719、地中海3232、美西2218、美东3128、波斯湾1981。</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="9" t="inlineStr">
+      <c r="A3" s="32" t="inlineStr">
         <is>
           <t>2026-01-16</t>
         </is>
       </c>
-      <c r="B3" s="10" t="n">
+      <c r="B3" s="12" t="n">
         <v>1574.12</v>
       </c>
-      <c r="C3" s="11" t="n">
+      <c r="C3" s="33" t="n">
         <v>-0.044476414206715</v>
       </c>
-      <c r="D3" s="10" t="n">
+      <c r="D3" s="12" t="n">
         <v>1188.42</v>
       </c>
-      <c r="E3" s="11" t="n">
-        <v>-0.007665330661322467</v>
-      </c>
-      <c r="F3" s="12" t="n">
+      <c r="E3" s="33" t="n">
+        <v>-0.00766533066132247</v>
+      </c>
+      <c r="F3" s="34" t="n">
         <v>1676</v>
       </c>
-      <c r="G3" s="12" t="n">
+      <c r="G3" s="34" t="n">
         <v>2983</v>
       </c>
-      <c r="H3" s="12" t="n">
+      <c r="H3" s="34" t="n">
         <v>2194</v>
       </c>
-      <c r="I3" s="12" t="n">
+      <c r="I3" s="34" t="n">
         <v>3165</v>
       </c>
-      <c r="J3" s="12" t="n">
+      <c r="J3" s="34" t="n">
         <v>1694</v>
       </c>
-      <c r="K3" s="13" t="inlineStr">
+      <c r="K3" s="35" t="inlineStr">
         <is>
           <t>90%-95%</t>
         </is>
       </c>
-      <c r="L3" s="14" t="inlineStr">
+      <c r="L3" s="36" t="inlineStr">
         <is>
           <t>SCFI报1574.12(-4.4%)。欧洲1676、地中海2983、美西2194、美东3165、波斯湾1694。</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
+      <c r="A4" s="27" t="inlineStr">
         <is>
           <t>2026-01-23</t>
         </is>
       </c>
-      <c r="B4" s="4" t="n">
+      <c r="B4" s="6" t="n">
         <v>1457.86</v>
       </c>
-      <c r="C4" s="5" t="n">
-        <v>-0.07385713922699666</v>
-      </c>
-      <c r="D4" s="4" t="n">
+      <c r="C4" s="28" t="n">
+        <v>-0.0738571392269967</v>
+      </c>
+      <c r="D4" s="6" t="n">
         <v>1175.59</v>
       </c>
-      <c r="E4" s="5" t="n">
+      <c r="E4" s="28" t="n">
         <v>-0.0107958465862239</v>
       </c>
-      <c r="F4" s="6" t="n">
+      <c r="F4" s="29" t="n">
         <v>1595</v>
       </c>
-      <c r="G4" s="6" t="n">
+      <c r="G4" s="29" t="n">
         <v>2756</v>
       </c>
-      <c r="H4" s="6" t="n">
+      <c r="H4" s="29" t="n">
         <v>2084</v>
       </c>
-      <c r="I4" s="6" t="n">
+      <c r="I4" s="29" t="n">
         <v>2896</v>
       </c>
-      <c r="J4" s="6" t="n">
+      <c r="J4" s="29" t="n">
         <v>1288</v>
       </c>
-      <c r="K4" s="7" t="inlineStr">
+      <c r="K4" s="30" t="inlineStr">
         <is>
           <t>90%</t>
         </is>
       </c>
-      <c r="L4" s="8" t="inlineStr">
+      <c r="L4" s="31" t="inlineStr">
         <is>
           <t>SCFI报1457.86(-7.4%)。欧洲1595、地中海2756、美西2084、美东2896、波斯湾1288。</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="9" t="inlineStr">
+      <c r="A5" s="32" t="inlineStr">
         <is>
           <t>2026-01-30</t>
         </is>
       </c>
-      <c r="B5" s="10" t="n">
+      <c r="B5" s="12" t="n">
         <v>1316.75</v>
       </c>
-      <c r="C5" s="11" t="n">
-        <v>-0.09679255895627836</v>
-      </c>
-      <c r="D5" s="10" t="n">
+      <c r="C5" s="33" t="n">
+        <v>-0.0967925589562784</v>
+      </c>
+      <c r="D5" s="12" t="n">
         <v>1152.3</v>
       </c>
-      <c r="E5" s="11" t="n">
-        <v>-0.01981132877959146</v>
-      </c>
-      <c r="F5" s="12" t="n">
+      <c r="E5" s="33" t="n">
+        <v>-0.0198113287795915</v>
+      </c>
+      <c r="F5" s="34" t="n">
         <v>1418</v>
       </c>
-      <c r="G5" s="12" t="n">
+      <c r="G5" s="34" t="n">
         <v>2424</v>
       </c>
-      <c r="H5" s="12" t="n">
+      <c r="H5" s="34" t="n">
         <v>1867</v>
       </c>
-      <c r="I5" s="12" t="n">
+      <c r="I5" s="34" t="n">
         <v>2605</v>
       </c>
-      <c r="J5" s="12" t="n">
+      <c r="J5" s="34" t="n">
         <v>997</v>
       </c>
-      <c r="K5" s="13" t="inlineStr">
+      <c r="K5" s="35" t="inlineStr">
         <is>
           <t>85%-90%</t>
         </is>
       </c>
-      <c r="L5" s="14" t="inlineStr">
+      <c r="L5" s="36" t="inlineStr">
         <is>
           <t>SCFI报1316.75(-9.7%)。欧洲1418、地中海2424、美西1867、美东2605、波斯湾997。</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="inlineStr">
+      <c r="A6" s="27" t="inlineStr">
         <is>
           <t>2026-02-06</t>
         </is>
       </c>
-      <c r="B6" s="4" t="n">
+      <c r="B6" s="6" t="n">
         <v>1266.56</v>
       </c>
-      <c r="C6" s="5" t="n">
-        <v>-0.03811657490032283</v>
-      </c>
-      <c r="D6" s="4" t="n">
+      <c r="C6" s="28" t="n">
+        <v>-0.0381165749003228</v>
+      </c>
+      <c r="D6" s="6" t="n">
         <v>1095.12</v>
       </c>
-      <c r="E6" s="5" t="n">
-        <v>-0.04962249414215059</v>
-      </c>
-      <c r="F6" s="6" t="n">
+      <c r="E6" s="28" t="n">
+        <v>-0.0496224941421506</v>
+      </c>
+      <c r="F6" s="29" t="n">
         <v>1403</v>
       </c>
-      <c r="G6" s="6" t="n">
+      <c r="G6" s="29" t="n">
         <v>2291</v>
       </c>
-      <c r="H6" s="6" t="n">
+      <c r="H6" s="29" t="n">
         <v>1801</v>
       </c>
-      <c r="I6" s="6" t="n">
+      <c r="I6" s="29" t="n">
         <v>2530</v>
       </c>
-      <c r="J6" s="6" t="n">
+      <c r="J6" s="29" t="n">
         <v>917</v>
       </c>
-      <c r="K6" s="7" t="inlineStr">
+      <c r="K6" s="30" t="inlineStr">
         <is>
           <t>80%-85%</t>
         </is>
       </c>
-      <c r="L6" s="8" t="inlineStr">
+      <c r="L6" s="31" t="inlineStr">
         <is>
           <t>SCFI报1266.56(-3.8%)。欧洲1403、地中海2291、美西1801、美东2530、波斯湾917。</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="9" t="inlineStr">
+      <c r="A7" s="32" t="inlineStr">
         <is>
           <t>2026-02-13</t>
         </is>
       </c>
-      <c r="B7" s="10" t="n">
+      <c r="B7" s="12" t="n">
         <v>1251.46</v>
       </c>
-      <c r="C7" s="11" t="n">
-        <v>-0.01192205659423939</v>
-      </c>
-      <c r="D7" s="10" t="n">
+      <c r="C7" s="33" t="n">
+        <v>-0.0119220565942394</v>
+      </c>
+      <c r="D7" s="12" t="n">
         <v>1068.3</v>
       </c>
-      <c r="E7" s="11" t="n">
-        <v>-0.02449046679815903</v>
-      </c>
-      <c r="F7" s="12" t="n">
+      <c r="E7" s="33" t="n">
+        <v>-0.024490466798159</v>
+      </c>
+      <c r="F7" s="34" t="n">
         <v>1361</v>
       </c>
-      <c r="G7" s="12" t="n">
+      <c r="G7" s="34" t="n">
         <v>2177</v>
       </c>
-      <c r="H7" s="12" t="n">
+      <c r="H7" s="34" t="n">
         <v>1787</v>
       </c>
-      <c r="I7" s="12" t="n">
+      <c r="I7" s="34" t="n">
         <v>2524</v>
       </c>
-      <c r="J7" s="12" t="n">
+      <c r="J7" s="34" t="n">
         <v>980</v>
       </c>
-      <c r="K7" s="13" t="inlineStr">
+      <c r="K7" s="35" t="inlineStr">
         <is>
           <t>80%</t>
         </is>
       </c>
-      <c r="L7" s="14" t="inlineStr">
+      <c r="L7" s="36" t="inlineStr">
         <is>
           <t>SCFI报1251.46(-1.2%)。欧洲1361、地中海2177、美西1787、美东2524、波斯湾980。</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="inlineStr">
+      <c r="A8" s="27" t="inlineStr">
         <is>
           <t>2026-02-27</t>
         </is>
       </c>
-      <c r="B8" s="4" t="n">
+      <c r="B8" s="6" t="n">
         <v>1333.11</v>
       </c>
-      <c r="C8" s="5" t="n">
-        <v>0.06524379524715118</v>
-      </c>
-      <c r="D8" s="4" t="n">
+      <c r="C8" s="28" t="n">
+        <v>0.0652437952471512</v>
+      </c>
+      <c r="D8" s="6" t="n">
         <v>1044.57</v>
       </c>
-      <c r="E8" s="5" t="n">
-        <v>-0.02221286155574276</v>
-      </c>
-      <c r="F8" s="6" t="n">
+      <c r="E8" s="28" t="n">
+        <v>-0.0222128615557428</v>
+      </c>
+      <c r="F8" s="29" t="n">
         <v>1420</v>
       </c>
-      <c r="G8" s="6" t="n">
+      <c r="G8" s="29" t="n">
         <v>2305</v>
       </c>
-      <c r="H8" s="6" t="n">
+      <c r="H8" s="29" t="n">
         <v>1857</v>
       </c>
-      <c r="I8" s="6" t="n">
+      <c r="I8" s="29" t="n">
         <v>2691</v>
       </c>
-      <c r="J8" s="6" t="n">
+      <c r="J8" s="29" t="n">
         <v>1327</v>
       </c>
-      <c r="K8" s="7" t="inlineStr">
+      <c r="K8" s="30" t="inlineStr">
         <is>
           <t>85%</t>
         </is>
       </c>
-      <c r="L8" s="8" t="inlineStr">
+      <c r="L8" s="31" t="inlineStr">
         <is>
           <t>SCFI报1333.11(+6.5%)。欧洲1420、地中海2305、美西1857、美东2691、波斯湾1327。</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="9" t="inlineStr">
+      <c r="A9" s="32" t="inlineStr">
         <is>
           <t>2026-03-06</t>
         </is>
       </c>
-      <c r="B9" s="10" t="n">
+      <c r="B9" s="12" t="n">
         <v>1489.19</v>
       </c>
-      <c r="C9" s="11" t="n">
-        <v>0.1170796108348149</v>
-      </c>
-      <c r="D9" s="10" t="n">
+      <c r="C9" s="33" t="n">
+        <v>0.117079610834815</v>
+      </c>
+      <c r="D9" s="12" t="n">
         <v>1054.26</v>
       </c>
-      <c r="E9" s="11" t="n">
-        <v>0.009276544415405485</v>
-      </c>
-      <c r="F9" s="12" t="n">
+      <c r="E9" s="33" t="n">
+        <v>0.009276544415405491</v>
+      </c>
+      <c r="F9" s="34" t="n">
         <v>1452</v>
       </c>
-      <c r="G9" s="12" t="n">
+      <c r="G9" s="34" t="n">
         <v>2360</v>
       </c>
-      <c r="H9" s="12" t="n">
+      <c r="H9" s="34" t="n">
         <v>1940</v>
       </c>
-      <c r="I9" s="12" t="n">
+      <c r="I9" s="34" t="n">
         <v>2717</v>
       </c>
-      <c r="J9" s="12" t="n">
+      <c r="J9" s="34" t="n">
         <v>2287</v>
       </c>
-      <c r="K9" s="13" t="inlineStr">
+      <c r="K9" s="35" t="inlineStr">
         <is>
           <t>90%-95%</t>
         </is>
       </c>
-      <c r="L9" s="14" t="inlineStr">
+      <c r="L9" s="36" t="inlineStr">
         <is>
           <t>SCFI报1489.19(+11.7%)。欧洲1452、地中海2360、美西1940、美东2717、波斯湾2287。</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="inlineStr">
+      <c r="A10" s="27" t="inlineStr">
         <is>
           <t>2026-03-13</t>
         </is>
       </c>
-      <c r="B10" s="4" t="n">
+      <c r="B10" s="6" t="n">
         <v>1710.35</v>
       </c>
-      <c r="C10" s="5" t="n">
-        <v>0.1485102639690032</v>
-      </c>
-      <c r="D10" s="4" t="n">
+      <c r="C10" s="28" t="n">
+        <v>0.148510263969003</v>
+      </c>
+      <c r="D10" s="6" t="n">
         <v>1072.15</v>
       </c>
-      <c r="E10" s="5" t="n">
-        <v>0.01696924857245841</v>
-      </c>
-      <c r="F10" s="6" t="n">
+      <c r="E10" s="28" t="n">
+        <v>0.0169692485724584</v>
+      </c>
+      <c r="F10" s="29" t="n">
         <v>1618</v>
       </c>
-      <c r="G10" s="6" t="n">
+      <c r="G10" s="29" t="n">
         <v>2666</v>
       </c>
-      <c r="H10" s="6" t="n">
+      <c r="H10" s="29" t="n">
         <v>2249</v>
       </c>
-      <c r="I10" s="6" t="n">
+      <c r="I10" s="29" t="n">
         <v>3111</v>
       </c>
-      <c r="J10" s="6" t="n">
+      <c r="J10" s="29" t="n">
         <v>3220</v>
       </c>
-      <c r="K10" s="7" t="inlineStr">
+      <c r="K10" s="30" t="inlineStr">
         <is>
           <t>&gt;95%</t>
         </is>
       </c>
-      <c r="L10" s="8" t="inlineStr">
+      <c r="L10" s="31" t="inlineStr">
         <is>
           <t>SCFI报1710.35(+14.9%)。欧洲1618、地中海2666、美西2249、美东3111、波斯湾3220。</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="9" t="inlineStr">
+      <c r="A11" s="32" t="inlineStr">
         <is>
           <t>2026-03-20</t>
         </is>
       </c>
-      <c r="B11" s="10" t="n">
+      <c r="B11" s="12" t="n">
         <v>1706.95</v>
       </c>
-      <c r="C11" s="11" t="n">
-        <v>-0.001987897214020484</v>
-      </c>
-      <c r="D11" s="10" t="n">
+      <c r="C11" s="33" t="n">
+        <v>-0.00198789721402048</v>
+      </c>
+      <c r="D11" s="12" t="n">
         <v>1110.82</v>
       </c>
-      <c r="E11" s="11" t="n">
-        <v>0.03606771440563339</v>
-      </c>
-      <c r="F11" s="12" t="n">
+      <c r="E11" s="33" t="n">
+        <v>0.0360677144056334</v>
+      </c>
+      <c r="F11" s="34" t="n">
         <v>1636</v>
       </c>
-      <c r="G11" s="12" t="n">
+      <c r="G11" s="34" t="n">
         <v>2784</v>
       </c>
-      <c r="H11" s="12" t="n">
+      <c r="H11" s="34" t="n">
         <v>2054</v>
       </c>
-      <c r="I11" s="12" t="n">
+      <c r="I11" s="34" t="n">
         <v>2922</v>
       </c>
-      <c r="J11" s="12" t="n">
+      <c r="J11" s="34" t="n">
         <v>3324</v>
       </c>
-      <c r="K11" s="13" t="inlineStr">
+      <c r="K11" s="35" t="inlineStr">
         <is>
           <t>~95%</t>
         </is>
       </c>
-      <c r="L11" s="14" t="inlineStr">
+      <c r="L11" s="36" t="inlineStr">
         <is>
           <t>SCFI报1706.95(-0.2%)。欧洲1636、地中海2784、美西2054、美东2922、波斯湾3324。</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="inlineStr">
+      <c r="A12" s="27" t="inlineStr">
         <is>
           <t>2026-03-27</t>
         </is>
       </c>
-      <c r="B12" s="4" t="n">
+      <c r="B12" s="6" t="n">
         <v>1826.77</v>
       </c>
-      <c r="C12" s="5" t="n">
-        <v>0.07019537772049556</v>
-      </c>
-      <c r="D12" s="4" t="n">
+      <c r="C12" s="28" t="n">
+        <v>0.0701953777204956</v>
+      </c>
+      <c r="D12" s="6" t="n">
         <v>1139.04</v>
       </c>
-      <c r="E12" s="5" t="n">
-        <v>0.02540465601987729</v>
-      </c>
-      <c r="F12" s="6" t="n">
+      <c r="E12" s="28" t="n">
+        <v>0.0254046560198773</v>
+      </c>
+      <c r="F12" s="29" t="n">
         <v>1703</v>
       </c>
-      <c r="G12" s="6" t="n">
+      <c r="G12" s="29" t="n">
         <v>2764</v>
       </c>
-      <c r="H12" s="6" t="n">
+      <c r="H12" s="29" t="n">
         <v>2352</v>
       </c>
-      <c r="I12" s="6" t="n">
+      <c r="I12" s="29" t="n">
         <v>3264</v>
       </c>
-      <c r="J12" s="6" t="n">
+      <c r="J12" s="29" t="n">
         <v>3728</v>
       </c>
-      <c r="K12" s="7" t="inlineStr">
+      <c r="K12" s="30" t="inlineStr">
         <is>
           <t>~98%</t>
         </is>
       </c>
-      <c r="L12" s="8" t="inlineStr">
+      <c r="L12" s="31" t="inlineStr">
         <is>
           <t>SCFI报1826.77(+7.0%)。欧洲1703、地中海2764、美西2352、美东3264、波斯湾3728。</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="9" t="inlineStr">
+      <c r="A13" s="32" t="inlineStr">
         <is>
           <t>2026-04-03</t>
         </is>
       </c>
-      <c r="B13" s="10" t="n">
+      <c r="B13" s="12" t="n">
         <v>1854.96</v>
       </c>
-      <c r="C13" s="11" t="n">
-        <v>0.01543160879585281</v>
-      </c>
-      <c r="D13" s="10" t="n">
+      <c r="C13" s="33" t="n">
+        <v>0.0154316087958528</v>
+      </c>
+      <c r="D13" s="12" t="n">
         <v>1182.45</v>
       </c>
-      <c r="E13" s="11" t="n">
-        <v>0.03811104087652772</v>
-      </c>
-      <c r="F13" s="12" t="n">
+      <c r="E13" s="33" t="n">
+        <v>0.0381110408765277</v>
+      </c>
+      <c r="F13" s="34" t="n">
         <v>1650</v>
       </c>
-      <c r="G13" s="12" t="n">
+      <c r="G13" s="34" t="n">
         <v>2684</v>
       </c>
-      <c r="H13" s="12" t="n">
+      <c r="H13" s="34" t="n">
         <v>2359</v>
       </c>
-      <c r="I13" s="12" t="n">
+      <c r="I13" s="34" t="n">
         <v>3354</v>
       </c>
-      <c r="J13" s="12" t="n">
+      <c r="J13" s="34" t="n">
         <v>3977</v>
       </c>
-      <c r="K13" s="13" t="inlineStr">
+      <c r="K13" s="35" t="inlineStr">
         <is>
           <t>~95%</t>
         </is>
       </c>
-      <c r="L13" s="14" t="inlineStr">
+      <c r="L13" s="36" t="inlineStr">
         <is>
           <t>SCFI报1854.96(+1.5%)。欧洲1650、地中海2684、美西2359、美东3354、波斯湾3977。</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="inlineStr">
+      <c r="A14" s="27" t="inlineStr">
         <is>
           <t>2026-04-10</t>
         </is>
       </c>
-      <c r="B14" s="4" t="n">
+      <c r="B14" s="6" t="n">
         <v>1890.77</v>
       </c>
-      <c r="C14" s="5" t="n">
-        <v>0.01930499849053335</v>
-      </c>
-      <c r="D14" s="4" t="n">
+      <c r="C14" s="28" t="n">
+        <v>0.0193049984905334</v>
+      </c>
+      <c r="D14" s="6" t="n">
         <v>1201.3</v>
       </c>
-      <c r="E14" s="5" t="n">
-        <v>0.01594147744090657</v>
-      </c>
-      <c r="F14" s="6" t="n">
+      <c r="E14" s="28" t="n">
+        <v>0.0159414774409066</v>
+      </c>
+      <c r="F14" s="29" t="n">
         <v>1547</v>
       </c>
-      <c r="G14" s="6" t="n">
+      <c r="G14" s="29" t="n">
         <v>2590</v>
       </c>
-      <c r="H14" s="6" t="n">
+      <c r="H14" s="29" t="n">
         <v>2552</v>
       </c>
-      <c r="I14" s="6" t="n">
+      <c r="I14" s="29" t="n">
         <v>3518</v>
       </c>
-      <c r="J14" s="6" t="n">
+      <c r="J14" s="29" t="n">
         <v>4167</v>
       </c>
-      <c r="K14" s="7" t="inlineStr">
+      <c r="K14" s="30" t="inlineStr">
         <is>
           <t>90%-95%</t>
         </is>
       </c>
-      <c r="L14" s="8" t="inlineStr">
+      <c r="L14" s="31" t="inlineStr">
         <is>
           <t>SCFI报1890.77(+1.9%)。欧洲1547、地中海2590、美西2552、美东3518、波斯湾4167。</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="9" t="inlineStr">
+      <c r="A15" s="32" t="inlineStr">
         <is>
           <t>2026-04-17</t>
         </is>
       </c>
-      <c r="B15" s="10" t="n">
+      <c r="B15" s="12" t="n">
         <v>1886.54</v>
       </c>
-      <c r="C15" s="11" t="n">
+      <c r="C15" s="33" t="n">
         <v>-0.00223718379284632</v>
       </c>
-      <c r="D15" s="10" t="n">
+      <c r="D15" s="12" t="n">
         <v>1220.18</v>
       </c>
-      <c r="E15" s="11" t="n">
-        <v>0.01571630733372187</v>
-      </c>
-      <c r="F15" s="12" t="n">
+      <c r="E15" s="33" t="n">
+        <v>0.0157163073337219</v>
+      </c>
+      <c r="F15" s="34" t="n">
         <v>1501</v>
       </c>
-      <c r="G15" s="12" t="n">
+      <c r="G15" s="34" t="n">
         <v>2491</v>
       </c>
-      <c r="H15" s="12" t="n">
+      <c r="H15" s="34" t="n">
         <v>2612</v>
       </c>
-      <c r="I15" s="12" t="n">
+      <c r="I15" s="34" t="n">
         <v>3584</v>
       </c>
-      <c r="J15" s="12" t="n">
+      <c r="J15" s="34" t="n">
         <v>4031</v>
       </c>
-      <c r="K15" s="13" t="inlineStr">
+      <c r="K15" s="35" t="inlineStr">
         <is>
           <t>~95%</t>
         </is>
       </c>
-      <c r="L15" s="14" t="inlineStr">
+      <c r="L15" s="36" t="inlineStr">
         <is>
           <t>SCFI报1886.54(-0.2%)。欧洲1501、地中海2491、美西2612、美东3584、波斯湾4031。</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="inlineStr">
+      <c r="A16" s="27" t="inlineStr">
         <is>
           <t>2026-04-24</t>
         </is>
       </c>
-      <c r="B16" s="4" t="n">
+      <c r="B16" s="6" t="n">
         <v>1875.26</v>
       </c>
-      <c r="C16" s="5" t="n">
-        <v>-0.005979200016962283</v>
-      </c>
-      <c r="D16" s="4" t="n">
+      <c r="C16" s="28" t="n">
+        <v>-0.00597920001696228</v>
+      </c>
+      <c r="D16" s="6" t="n">
         <v>1233.76</v>
       </c>
-      <c r="E16" s="5" t="n">
-        <v>0.01112950548279756</v>
-      </c>
-      <c r="F16" s="6" t="n">
+      <c r="E16" s="28" t="n">
+        <v>0.0111295054827976</v>
+      </c>
+      <c r="F16" s="29" t="n">
         <v>1497</v>
       </c>
-      <c r="G16" s="6" t="n">
+      <c r="G16" s="29" t="n">
         <v>2420</v>
       </c>
-      <c r="H16" s="6" t="n">
+      <c r="H16" s="29" t="n">
         <v>2586</v>
       </c>
-      <c r="I16" s="6" t="n">
+      <c r="I16" s="29" t="n">
         <v>3570</v>
       </c>
-      <c r="J16" s="6" t="n">
+      <c r="J16" s="29" t="n">
         <v>3951</v>
       </c>
-      <c r="K16" s="7" t="inlineStr">
+      <c r="K16" s="30" t="inlineStr">
         <is>
           <t>&gt;95%</t>
         </is>
       </c>
-      <c r="L16" s="8" t="inlineStr">
+      <c r="L16" s="31" t="inlineStr">
         <is>
           <t>SCFI报1875.26(-0.6%)。欧洲1497、地中海2420、美西2586、美东3570、波斯湾3951。</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="9" t="inlineStr">
+      <c r="A17" s="32" t="inlineStr">
         <is>
           <t>2026-04-30</t>
         </is>
       </c>
-      <c r="B17" s="10" t="n">
+      <c r="B17" s="12" t="n">
         <v>1911.4</v>
       </c>
-      <c r="C17" s="11" t="n">
-        <v>0.01927199428345938</v>
-      </c>
-      <c r="D17" s="10" t="n">
+      <c r="C17" s="33" t="n">
+        <v>0.0192719942834594</v>
+      </c>
+      <c r="D17" s="12" t="n">
         <v>1245.9</v>
       </c>
-      <c r="E17" s="11" t="n">
-        <v>0.009839839190766586</v>
-      </c>
-      <c r="F17" s="12" t="n">
+      <c r="E17" s="33" t="n">
+        <v>0.00983983919076659</v>
+      </c>
+      <c r="F17" s="34" t="n">
         <v>1521</v>
       </c>
-      <c r="G17" s="12" t="n">
+      <c r="G17" s="34" t="n">
         <v>2430</v>
       </c>
-      <c r="H17" s="12" t="n">
+      <c r="H17" s="34" t="n">
         <v>2722</v>
       </c>
-      <c r="I17" s="12" t="n">
+      <c r="I17" s="34" t="n">
         <v>3691</v>
       </c>
-      <c r="J17" s="12" t="n">
+      <c r="J17" s="34" t="n">
         <v>3937</v>
       </c>
-      <c r="K17" s="13" t="inlineStr">
+      <c r="K17" s="35" t="inlineStr">
         <is>
           <t>~100%</t>
         </is>
       </c>
-      <c r="L17" s="14" t="inlineStr">
+      <c r="L17" s="36" t="inlineStr">
         <is>
           <t>SCFI报1911.4(+1.9%)。欧洲1521、地中海2430、美西2722、美东3691、波斯湾3937。</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="3" t="inlineStr">
+      <c r="A18" s="27" t="inlineStr">
         <is>
           <t>2026-05-08</t>
         </is>
       </c>
-      <c r="B18" s="4" t="n">
+      <c r="B18" s="6" t="n">
         <v>1954.21</v>
       </c>
-      <c r="C18" s="5" t="n">
-        <v>0.02239719577273203</v>
-      </c>
-      <c r="D18" s="4" t="n">
+      <c r="C18" s="28" t="n">
+        <v>0.022397195772732</v>
+      </c>
+      <c r="D18" s="6" t="n">
         <v>1278.79</v>
       </c>
-      <c r="E18" s="5" t="n">
+      <c r="E18" s="28" t="n">
         <v>0.0263985873665622</v>
       </c>
-      <c r="F18" s="6" t="n">
+      <c r="F18" s="29" t="n">
         <v>1596</v>
       </c>
-      <c r="G18" s="6" t="n">
+      <c r="G18" s="29" t="n">
         <v>2463</v>
       </c>
-      <c r="H18" s="6" t="n">
+      <c r="H18" s="29" t="n">
         <v>2826</v>
       </c>
-      <c r="I18" s="6" t="n">
+      <c r="I18" s="29" t="n">
         <v>3812</v>
       </c>
-      <c r="J18" s="6" t="n">
+      <c r="J18" s="29" t="n">
         <v>3925</v>
       </c>
-      <c r="K18" s="7" t="inlineStr">
+      <c r="K18" s="30" t="inlineStr">
         <is>
           <t>95%-100%</t>
         </is>
       </c>
-      <c r="L18" s="8" t="inlineStr">
+      <c r="L18" s="31" t="inlineStr">
         <is>
           <t>SCFI报1954.21(+2.2%)。欧洲1596、地中海2463、美西2826、美东3812、波斯湾3925。</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="9" t="inlineStr">
+      <c r="A19" s="32" t="inlineStr">
         <is>
           <t>2026-05-15</t>
         </is>
       </c>
-      <c r="B19" s="10" t="n">
+      <c r="B19" s="12" t="n">
         <v>2140.66</v>
       </c>
-      <c r="C19" s="11" t="n">
-        <v>0.09540939817112792</v>
-      </c>
-      <c r="D19" s="10" t="n">
+      <c r="C19" s="33" t="n">
+        <v>0.0954093981711279</v>
+      </c>
+      <c r="D19" s="12" t="n">
         <v>1310.2</v>
       </c>
-      <c r="E19" s="11" t="n">
-        <v>0.02456228153176054</v>
-      </c>
-      <c r="F19" s="12" t="n">
+      <c r="E19" s="33" t="n">
+        <v>0.0245622815317605</v>
+      </c>
+      <c r="F19" s="34" t="n">
         <v>1816</v>
       </c>
-      <c r="G19" s="12" t="n">
+      <c r="G19" s="34" t="n">
         <v>3145</v>
       </c>
-      <c r="H19" s="12" t="n">
+      <c r="H19" s="34" t="n">
         <v>3118</v>
       </c>
-      <c r="I19" s="12" t="n">
+      <c r="I19" s="34" t="n">
         <v>4224</v>
       </c>
-      <c r="J19" s="12" t="n">
+      <c r="J19" s="34" t="n">
         <v>4131</v>
       </c>
-      <c r="K19" s="13" t="inlineStr">
+      <c r="K19" s="35" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="L19" s="14" t="inlineStr">
+      <c r="L19" s="36" t="inlineStr">
         <is>
           <t>SCFI报2140.66(+9.5%)。欧洲1816、地中海3145、美西3118、美东4224、波斯湾4131。</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="3" t="inlineStr">
+      <c r="A20" s="27" t="inlineStr">
         <is>
           <t>2026-05-22</t>
         </is>
       </c>
-      <c r="B20" s="4" t="n">
+      <c r="B20" s="6" t="n">
         <v>2218.15</v>
       </c>
-      <c r="C20" s="5" t="n">
+      <c r="C20" s="28" t="n">
         <v>0.0361991161604367</v>
       </c>
-      <c r="D20" s="4" t="n">
+      <c r="D20" s="6" t="n">
         <v>1332.1</v>
       </c>
-      <c r="E20" s="5" t="n">
-        <v>0.01671500534269565</v>
-      </c>
-      <c r="F20" s="6" t="n">
+      <c r="E20" s="28" t="n">
+        <v>0.0167150053426957</v>
+      </c>
+      <c r="F20" s="29" t="n">
         <v>1905</v>
       </c>
-      <c r="G20" s="6" t="n">
+      <c r="G20" s="29" t="n">
         <v>3207</v>
       </c>
-      <c r="H20" s="6" t="n">
+      <c r="H20" s="29" t="n">
         <v>3154</v>
       </c>
-      <c r="I20" s="6" t="n">
+      <c r="I20" s="29" t="n">
         <v>4313</v>
       </c>
-      <c r="J20" s="6" t="n">
+      <c r="J20" s="29" t="n">
         <v>4306</v>
       </c>
-      <c r="K20" s="7" t="inlineStr">
+      <c r="K20" s="30" t="inlineStr">
         <is>
           <t>&gt;95%</t>
         </is>
       </c>
-      <c r="L20" s="8" t="inlineStr">
+      <c r="L20" s="31" t="inlineStr">
         <is>
           <t>SCFI报2218.15(+3.6%)。欧洲1905、地中海3207、美西3154、美东4313、波斯湾4306。</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="9" t="inlineStr">
+      <c r="A21" s="32" t="inlineStr">
         <is>
           <t>2026-05-29</t>
         </is>
       </c>
-      <c r="B21" s="10" t="n">
+      <c r="B21" s="12" t="n">
         <v>2571.73</v>
       </c>
-      <c r="C21" s="11" t="n">
-        <v>0.1594031061920971</v>
-      </c>
-      <c r="D21" s="10" t="n">
+      <c r="C21" s="33" t="n">
+        <v>0.159403106192097</v>
+      </c>
+      <c r="D21" s="12" t="n">
         <v>1366.76</v>
       </c>
-      <c r="E21" s="11" t="n">
+      <c r="E21" s="33" t="n">
         <v>0.0260190676375649</v>
       </c>
-      <c r="F21" s="12" t="n">
+      <c r="F21" s="34" t="n">
         <v>2475</v>
       </c>
-      <c r="G21" s="12" t="n">
+      <c r="G21" s="34" t="n">
         <v>3750</v>
       </c>
-      <c r="H21" s="12" t="n">
+      <c r="H21" s="34" t="n">
         <v>4149</v>
       </c>
-      <c r="I21" s="12" t="n">
+      <c r="I21" s="34" t="n">
         <v>5333</v>
       </c>
-      <c r="J21" s="12" t="n">
+      <c r="J21" s="34" t="n">
         <v>4462</v>
       </c>
-      <c r="K21" s="13" t="inlineStr">
+      <c r="K21" s="35" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="L21" s="14" t="inlineStr">
+      <c r="L21" s="36" t="inlineStr">
         <is>
           <t>SCFI报2571.73(+15.9%)。欧洲2475、地中海3750、美西4149、美东5333、波斯湾4462。</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="3" t="inlineStr">
+      <c r="A22" s="27" t="inlineStr">
         <is>
           <t>2026-06-05</t>
         </is>
       </c>
-      <c r="B22" s="4" t="n">
+      <c r="B22" s="6" t="n">
         <v>2726.48</v>
       </c>
-      <c r="C22" s="5" t="n">
-        <v>0.06017350188394577</v>
-      </c>
-      <c r="D22" s="4" t="n">
+      <c r="C22" s="28" t="n">
+        <v>0.0601735018839458</v>
+      </c>
+      <c r="D22" s="6" t="n">
         <v>1412.3</v>
       </c>
-      <c r="E22" s="5" t="n">
-        <v>0.03331967572946226</v>
-      </c>
-      <c r="F22" s="6" t="n">
+      <c r="E22" s="28" t="n">
+        <v>0.0333196757294623</v>
+      </c>
+      <c r="F22" s="29" t="n">
         <v>2605</v>
       </c>
-      <c r="G22" s="6" t="n">
+      <c r="G22" s="29" t="n">
         <v>3832</v>
       </c>
-      <c r="H22" s="6" t="n">
+      <c r="H22" s="29" t="n">
         <v>4552</v>
       </c>
-      <c r="I22" s="6" t="n">
+      <c r="I22" s="29" t="n">
         <v>5741</v>
       </c>
-      <c r="J22" s="6" t="n">
+      <c r="J22" s="29" t="n">
         <v>4615</v>
       </c>
-      <c r="K22" s="7" t="inlineStr">
+      <c r="K22" s="30" t="inlineStr">
         <is>
           <t>95%-100%</t>
         </is>
       </c>
-      <c r="L22" s="8" t="inlineStr">
+      <c r="L22" s="31" t="inlineStr">
         <is>
           <t>SCFI报2726.48(+6.0%)。欧洲2605、地中海3832、美西4552、美东5741、波斯湾4615。</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="9" t="inlineStr">
+      <c r="A23" s="32" t="inlineStr">
         <is>
           <t>2026-06-12</t>
         </is>
       </c>
-      <c r="B23" s="10" t="n">
+      <c r="B23" s="12" t="n">
         <v>2985.22</v>
       </c>
-      <c r="C23" s="11" t="n">
-        <v>0.09489891728529076</v>
-      </c>
-      <c r="D23" s="10" t="n">
+      <c r="C23" s="33" t="n">
+        <v>0.0948989172852908</v>
+      </c>
+      <c r="D23" s="12" t="n">
         <v>1480.11</v>
       </c>
-      <c r="E23" s="11" t="n">
-        <v>0.04801387807123136</v>
-      </c>
-      <c r="F23" s="12" t="n">
+      <c r="E23" s="33" t="n">
+        <v>0.0480138780712314</v>
+      </c>
+      <c r="F23" s="34" t="n">
         <v>3064</v>
       </c>
-      <c r="G23" s="12" t="n">
+      <c r="G23" s="34" t="n">
         <v>4172</v>
       </c>
-      <c r="H23" s="12" t="n">
+      <c r="H23" s="34" t="n">
         <v>5101</v>
       </c>
-      <c r="I23" s="12" t="n">
+      <c r="I23" s="34" t="n">
         <v>6321</v>
       </c>
-      <c r="J23" s="12" t="n">
+      <c r="J23" s="34" t="n">
         <v>4816</v>
       </c>
-      <c r="K23" s="13" t="inlineStr">
+      <c r="K23" s="35" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="L23" s="14" t="inlineStr">
+      <c r="L23" s="36" t="inlineStr">
         <is>
           <t>SCFI报2985.22(+9.5%)。欧洲3064、地中海4172、美西5101、美东6321、波斯湾4816。</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="9" t="inlineStr">
+      <c r="A24" s="32" t="inlineStr">
         <is>
           <t>2026-06-26</t>
         </is>
       </c>
-      <c r="B24" s="10" t="n">
+      <c r="B24" s="12" t="n">
         <v>3239.64</v>
       </c>
-      <c r="C24" s="11" t="n">
+      <c r="C24" s="33" t="n">
         <v>0.085226549467041</v>
       </c>
-      <c r="D24" s="10" t="n">
+      <c r="D24" s="12" t="n">
         <v>1710.47</v>
       </c>
-      <c r="E24" s="11" t="n">
-        <v>0.1556370810277616</v>
-      </c>
-      <c r="F24" s="12" t="n">
+      <c r="E24" s="33" t="n">
+        <v>0.155637081027762</v>
+      </c>
+      <c r="F24" s="34" t="n">
         <v>3342</v>
       </c>
-      <c r="G24" s="12" t="n">
+      <c r="G24" s="34" t="n">
         <v>4666</v>
       </c>
-      <c r="H24" s="12" t="n">
+      <c r="H24" s="34" t="n">
         <v>6067</v>
       </c>
-      <c r="I24" s="12" t="n">
+      <c r="I24" s="34" t="n">
         <v>7384</v>
       </c>
-      <c r="J24" s="12" t="n">
+      <c r="J24" s="34" t="n">
         <v>4592</v>
       </c>
-      <c r="K24" s="13" t="inlineStr">
+      <c r="K24" s="35" t="inlineStr">
         <is>
           <t>95%-100%</t>
         </is>
       </c>
-      <c r="L24" s="14" t="inlineStr">
+      <c r="L24" s="36" t="inlineStr">
         <is>
           <t>SCFI报3239.64(+8.5%)。欧洲3342、地中海4666、美西6067、美东7384、波斯湾4592。</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="3" t="inlineStr">
+      <c r="A25" s="27" t="inlineStr">
         <is>
           <t>2026-07-03</t>
         </is>
       </c>
-      <c r="B25" s="4" t="n">
+      <c r="B25" s="6" t="n">
         <v>3326.87</v>
       </c>
-      <c r="C25" s="5" t="n">
-        <v>0.02692583126520232</v>
-      </c>
-      <c r="D25" s="4" t="n">
+      <c r="C25" s="28" t="n">
+        <v>0.0269258312652023</v>
+      </c>
+      <c r="D25" s="6" t="n">
         <v>1811.5</v>
       </c>
-      <c r="E25" s="5" t="n">
+      <c r="E25" s="28" t="n">
         <v>0.0590656369302005</v>
       </c>
-      <c r="F25" s="6" t="n">
+      <c r="F25" s="29" t="n">
         <v>3418</v>
       </c>
-      <c r="G25" s="6" t="n">
+      <c r="G25" s="29" t="n">
         <v>4717</v>
       </c>
-      <c r="H25" s="6" t="n">
+      <c r="H25" s="29" t="n">
         <v>6630</v>
       </c>
-      <c r="I25" s="6" t="n">
+      <c r="I25" s="29" t="n">
         <v>8296</v>
       </c>
-      <c r="J25" s="6" t="n">
+      <c r="J25" s="29" t="n">
         <v>4392</v>
       </c>
-      <c r="K25" s="7" t="inlineStr">
+      <c r="K25" s="30" t="inlineStr">
         <is>
           <t>95%-100%</t>
         </is>
       </c>
-      <c r="L25" s="8" t="inlineStr">
+      <c r="L25" s="31" t="inlineStr">
         <is>
           <t>SCFI报3326.87(+2.7%)。欧洲3418、地中海4717、美西6630、美东8296、波斯湾4392。</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="9" t="inlineStr">
+      <c r="A26" s="32" t="inlineStr">
         <is>
           <t>2026-07-10</t>
         </is>
       </c>
-      <c r="B26" s="10" t="n">
+      <c r="B26" s="12" t="n">
         <v>3184.82</v>
       </c>
-      <c r="C26" s="11" t="n">
-        <v>-0.04269779101678151</v>
-      </c>
-      <c r="D26" s="10" t="n">
+      <c r="C26" s="33" t="n">
+        <v>-0.0426977910167815</v>
+      </c>
+      <c r="D26" s="12" t="n">
         <v>1873.15</v>
       </c>
-      <c r="E26" s="11" t="n">
-        <v>0.03403256969362412</v>
-      </c>
-      <c r="F26" s="12" t="n">
+      <c r="E26" s="33" t="n">
+        <v>0.0340325696936241</v>
+      </c>
+      <c r="F26" s="34" t="n">
         <v>3332</v>
       </c>
-      <c r="G26" s="12" t="n">
+      <c r="G26" s="34" t="n">
         <v>4561</v>
       </c>
-      <c r="H26" s="12" t="n">
+      <c r="H26" s="34" t="n">
         <v>6219</v>
       </c>
-      <c r="I26" s="12" t="n">
+      <c r="I26" s="34" t="n">
         <v>8134</v>
       </c>
-      <c r="J26" s="12" t="n">
+      <c r="J26" s="34" t="n">
         <v>4199</v>
       </c>
-      <c r="K26" s="13" t="inlineStr">
+      <c r="K26" s="35" t="inlineStr">
         <is>
           <t>~95%</t>
         </is>
       </c>
-      <c r="L26" s="14" t="inlineStr">
+      <c r="L26" s="36" t="inlineStr">
         <is>
           <t>SCFI报3184.82(-4.3%)。欧洲3332、地中海4561、美西6219、美东8134、波斯湾4199。</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="3" t="inlineStr">
+      <c r="A27" s="27" t="inlineStr">
         <is>
           <t>2026-07-17</t>
         </is>
       </c>
-      <c r="B27" s="4" t="n">
+      <c r="B27" s="6" t="n">
         <v>3080.31</v>
       </c>
-      <c r="C27" s="5" t="n">
-        <v>-0.03281504135241564</v>
-      </c>
-      <c r="D27" s="4" t="n">
+      <c r="C27" s="28" t="n">
+        <v>-0.0328150413524157</v>
+      </c>
+      <c r="D27" s="6" t="n">
         <v>1910.67</v>
       </c>
-      <c r="E27" s="5" t="n">
-        <v>0.02003043002429061</v>
-      </c>
-      <c r="F27" s="6" t="n">
+      <c r="E27" s="28" t="n">
+        <v>0.0200304300242906</v>
+      </c>
+      <c r="F27" s="29" t="n">
         <v>3215</v>
       </c>
-      <c r="G27" s="6" t="n">
+      <c r="G27" s="29" t="n">
         <v>4475</v>
       </c>
-      <c r="H27" s="6" t="n">
+      <c r="H27" s="29" t="n">
         <v>5721</v>
       </c>
-      <c r="I27" s="6" t="n">
+      <c r="I27" s="29" t="n">
         <v>8172</v>
       </c>
-      <c r="J27" s="6" t="n">
+      <c r="J27" s="29" t="n">
         <v>4266</v>
       </c>
-      <c r="K27" s="7" t="inlineStr">
+      <c r="K27" s="30" t="inlineStr">
         <is>
           <t>90%-95%</t>
         </is>
       </c>
-      <c r="L27" s="8" t="inlineStr">
+      <c r="L27" s="31" t="inlineStr">
         <is>
           <t>SCFI报3080.31(-3.3%)。欧洲3215、地中海4475、美西5721、美东8172、波斯湾4266。</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="9" t="inlineStr">
+      <c r="A28" s="32" t="inlineStr">
         <is>
           <t>2026-07-24</t>
         </is>
       </c>
-      <c r="B28" s="10" t="n">
+      <c r="B28" s="12" t="n">
         <v>3062.95</v>
       </c>
-      <c r="C28" s="11" t="n">
-        <v>-0.005635796397115866</v>
-      </c>
-      <c r="D28" s="10" t="n">
+      <c r="C28" s="33" t="n">
+        <v>-0.00563579639711587</v>
+      </c>
+      <c r="D28" s="12" t="n">
         <v>1901.27</v>
       </c>
-      <c r="E28" s="11" t="n">
-        <v>-0.004919740195847622</v>
-      </c>
-      <c r="F28" s="12" t="n">
+      <c r="E28" s="33" t="n">
+        <v>-0.00491974019584762</v>
+      </c>
+      <c r="F28" s="34" t="n">
         <v>3155</v>
       </c>
-      <c r="G28" s="12" t="n">
+      <c r="G28" s="34" t="n">
         <v>4351</v>
       </c>
-      <c r="H28" s="12" t="n">
+      <c r="H28" s="34" t="n">
         <v>5535</v>
       </c>
-      <c r="I28" s="12" t="n">
+      <c r="I28" s="34" t="n">
         <v>8040</v>
       </c>
-      <c r="J28" s="12" t="n">
+      <c r="J28" s="34" t="n">
         <v>4584</v>
       </c>
-      <c r="K28" s="13" t="inlineStr">
+      <c r="K28" s="35" t="inlineStr">
         <is>
           <t>&gt;90%</t>
         </is>
       </c>
-      <c r="L28" s="14" t="inlineStr">
+      <c r="L28" s="36" t="inlineStr">
         <is>
           <t>SCFI报3062.95(-0.6%)。欧洲3155、地中海4351、美西5535、美东8040、波斯湾4584。</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="3" t="inlineStr">
+      <c r="A29" s="27" t="inlineStr">
         <is>
           <t>2026-07-31</t>
         </is>
       </c>
-      <c r="B29" s="4" t="n">
+      <c r="B29" s="6" t="n">
         <v>3205.97</v>
       </c>
-      <c r="C29" s="5" t="n">
-        <v>0.04669354707063444</v>
-      </c>
-      <c r="D29" s="4" t="n">
+      <c r="C29" s="28" t="n">
+        <v>0.0466935470706344</v>
+      </c>
+      <c r="D29" s="6" t="n">
         <v>1857.04</v>
       </c>
-      <c r="E29" s="5" t="n">
-        <v>-0.02326339762369367</v>
-      </c>
-      <c r="F29" s="6" t="n">
+      <c r="E29" s="28" t="n">
+        <v>-0.0232633976236937</v>
+      </c>
+      <c r="F29" s="29" t="n">
         <v>3039</v>
       </c>
-      <c r="G29" s="6" t="n">
+      <c r="G29" s="29" t="n">
         <v>4189</v>
       </c>
-      <c r="H29" s="6" t="n">
+      <c r="H29" s="37" t="n">
         <v>6229</v>
       </c>
-      <c r="I29" s="6" t="n">
+      <c r="I29" s="29" t="n">
         <v>9054</v>
       </c>
-      <c r="J29" s="6" t="n">
+      <c r="J29" s="29" t="n">
         <v>4894</v>
       </c>
-      <c r="K29" s="7" t="inlineStr">
+      <c r="K29" s="30" t="inlineStr">
         <is>
           <t>&gt;95%</t>
         </is>
       </c>
-      <c r="L29" s="8" t="inlineStr">
+      <c r="L29" s="31" t="inlineStr">
         <is>
           <t>SCFI报3205.97(+4.7%)。欧洲3039、地中海4189、美西6229、美东9054、波斯湾4894。</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" t="inlineStr">
+      <c r="A30" s="27" t="inlineStr">
         <is>
           <t>2026-08-07</t>
         </is>
       </c>
-      <c r="B30" s="20" t="n">
+      <c r="B30" s="6" t="n">
         <v>3276.14</v>
       </c>
-      <c r="C30" s="19" t="n">
-        <v>0.02188729152175473</v>
-      </c>
-      <c r="D30" s="20" t="n">
+      <c r="C30" s="28" t="n">
+        <v>0.0218872915217547</v>
+      </c>
+      <c r="D30" s="6" t="n">
         <v>1839.61</v>
       </c>
-      <c r="E30" s="19" t="n">
-        <v>-0.009385904450092686</v>
-      </c>
-      <c r="F30" s="18" t="n">
+      <c r="E30" s="28" t="n">
+        <v>-0.009385904450092689</v>
+      </c>
+      <c r="F30" s="29" t="n">
         <v>2964</v>
       </c>
-      <c r="G30" s="18" t="n">
+      <c r="G30" s="29" t="n">
         <v>4048</v>
       </c>
-      <c r="H30" s="18" t="n">
+      <c r="H30" s="29" t="n">
         <v>6484</v>
       </c>
-      <c r="I30" s="18" t="n">
+      <c r="I30" s="29" t="n">
         <v>9290</v>
       </c>
-      <c r="J30" s="18" t="n">
+      <c r="J30" s="29" t="n">
         <v>5258</v>
       </c>
-      <c r="K30" t="inlineStr">
+      <c r="K30" s="30" t="inlineStr">
         <is>
           <t>&gt;95%</t>
         </is>
       </c>
-      <c r="L30" t="inlineStr">
+      <c r="L30" s="31" t="inlineStr">
         <is>
           <t>SCFI报3276.14(+2.2%)。欧洲2964、地中海4048、美西6484、美东9290、波斯湾5258。</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" t="inlineStr">
+      <c r="A31" s="27" t="inlineStr">
         <is>
           <t>2026-08-14</t>
         </is>
       </c>
-      <c r="B31" s="20" t="n">
+      <c r="B31" s="6" t="n">
         <v>3355.24</v>
       </c>
-      <c r="C31" s="19" t="n">
+      <c r="C31" s="28" t="n">
         <v>0.024</v>
       </c>
-      <c r="D31" s="20" t="n">
+      <c r="D31" s="6" t="n">
         <v>1846.96</v>
       </c>
-      <c r="E31" s="19" t="n">
+      <c r="E31" s="28" t="n">
         <v>0.004</v>
       </c>
-      <c r="F31" s="18" t="n">
+      <c r="F31" s="29" t="n">
         <v>2945</v>
       </c>
-      <c r="G31" s="18" t="n">
+      <c r="G31" s="29" t="n">
         <v>3929</v>
       </c>
-      <c r="H31" s="18" t="n">
+      <c r="H31" s="29" t="n">
         <v>6714</v>
       </c>
-      <c r="I31" s="18" t="n">
+      <c r="I31" s="29" t="n">
         <v>9568</v>
       </c>
-      <c r="J31" s="18" t="n">
+      <c r="J31" s="29" t="n">
         <v>5422</v>
       </c>
-      <c r="K31" t="inlineStr">
+      <c r="K31" s="30" t="inlineStr">
         <is>
           <t>&gt;95%</t>
         </is>
       </c>
-      <c r="L31" t="inlineStr">
+      <c r="L31" s="31" t="inlineStr">
         <is>
           <t>SCFI报3355.24(+2.4%)，CCFI报1846.96(+0.4%)。欧洲2945(-0.6%)、地中海3929(-2.9%)回落；美西6714(+3.5%)、美东9568(+3.0%)上涨；波斯湾5422(+3.1%)因中东紧张续涨。</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" t="inlineStr">
+      <c r="A32" s="27" t="inlineStr">
         <is>
           <t>2026-08-21</t>
         </is>
       </c>
-      <c r="B32" t="n">
+      <c r="B32" s="6" t="n">
         <v>3409.63</v>
       </c>
-      <c r="C32" t="n">
+      <c r="C32" s="28" t="n">
         <v>0.016</v>
       </c>
-      <c r="D32" t="n">
+      <c r="D32" s="6" t="n">
         <v>1821.65</v>
       </c>
-      <c r="E32" t="n">
+      <c r="E32" s="28" t="n">
         <v>-0.014</v>
       </c>
-      <c r="F32" t="n">
+      <c r="F32" s="29" t="n">
         <v>2842</v>
       </c>
-      <c r="G32" t="n">
+      <c r="G32" s="29" t="n">
         <v>3767</v>
       </c>
-      <c r="H32" t="n">
+      <c r="H32" s="29" t="n">
         <v>6765</v>
       </c>
-      <c r="I32" t="n">
+      <c r="I32" s="29" t="n">
         <v>9700</v>
       </c>
-      <c r="J32" t="n">
+      <c r="J32" s="29" t="n">
         <v>5729</v>
       </c>
-      <c r="K32" t="inlineStr">
+      <c r="K32" s="30" t="inlineStr">
         <is>
           <t>&gt;95%</t>
         </is>
       </c>
-      <c r="L32" t="inlineStr">
+      <c r="L32" s="31" t="inlineStr">
         <is>
           <t>SCFI报3409.63(+1.6%)，CCFI报1821.65(-1.4%)。欧洲2842(-3.5%)、地中海3767(-4.1%)回落；美西6765(+0.8%)、美东9700(+1.4%)上涨；波斯湾5729(+5.7%)因中东紧张续涨。</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" t="inlineStr">
+      <c r="A33" s="27" t="inlineStr">
         <is>
           <t>2026-08-28</t>
         </is>
       </c>
-      <c r="B33" t="n">
+      <c r="B33" s="6" t="n">
         <v>3509.53</v>
       </c>
-      <c r="C33" t="n">
+      <c r="C33" s="28" t="n">
         <v>0.029</v>
       </c>
-      <c r="D33" t="n">
+      <c r="D33" s="6" t="n">
         <v>1833.99</v>
       </c>
-      <c r="E33" t="n">
+      <c r="E33" s="28" t="n">
         <v>0.007</v>
       </c>
-      <c r="F33" t="n">
+      <c r="F33" s="29" t="n">
         <v>2716</v>
       </c>
-      <c r="G33" t="n">
+      <c r="G33" s="29" t="n">
         <v>3557</v>
       </c>
-      <c r="H33" t="n">
+      <c r="H33" s="29" t="n">
         <v>6940</v>
       </c>
-      <c r="I33" t="n">
+      <c r="I33" s="29" t="n">
         <v>10046</v>
       </c>
-      <c r="J33" t="n">
+      <c r="J33" s="29" t="n">
         <v>6139</v>
       </c>
-      <c r="K33" t="inlineStr">
+      <c r="K33" s="30" t="inlineStr">
         <is>
           <t>&gt;95%</t>
         </is>
       </c>
-      <c r="L33" t="inlineStr">
+      <c r="L33" s="31" t="inlineStr">
         <is>
           <t>SCFI报3509.53(+2.9%)，CCFI报1833.99(+0.7%)。欧洲2716(-4.4%)、地中海3557(-5.6%)继续回落；美西6940(+2.6%)、美东10046(+3.6%)受巴拿马运河水位下降、舱位紧张带动续涨；波斯湾6139(+7.1%)大幅反弹；澳新2471(+6.7%)、南美8663(+11.0%)同步上涨。</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="27" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B34" s="6" t="n">
+        <v>3590.05</v>
+      </c>
+      <c r="C34" s="28" t="n">
+        <v>0.023</v>
+      </c>
+      <c r="D34" s="6" t="n">
+        <v>1837.01</v>
+      </c>
+      <c r="E34" s="28" t="n">
+        <v>0.0016</v>
+      </c>
+      <c r="F34" s="29" t="n">
+        <v>2643</v>
+      </c>
+      <c r="G34" s="29" t="n">
+        <v>3442</v>
+      </c>
+      <c r="H34" s="29" t="n">
+        <v>7242</v>
+      </c>
+      <c r="I34" s="29" t="n">
+        <v>10324</v>
+      </c>
+      <c r="J34" s="29" t="n">
+        <v>6135</v>
+      </c>
+      <c r="K34" s="30" t="inlineStr">
+        <is>
+          <t>&gt;95%</t>
+        </is>
+      </c>
+      <c r="L34" s="31" t="inlineStr">
+        <is>
+          <t>SCFI报3590.05(+2.3%)，CCFI报1837.01(+0.2%)。欧洲2643(-2.7%)、地中海3442(-3.2%)继续回落；美西7242(+4.4%)、美东10324(+2.8%)受需求高位、舱位紧张带动续涨；波斯湾6135(-0.1%)平稳；澳新2640(+6.8%)、南美8953(+3.3%)同步上涨。</t>
         </is>
       </c>
     </row>
@@ -2017,587 +2137,587 @@
   <dimension ref="A1:H20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="13" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="27" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="20" customWidth="1" min="6" max="6"/>
-    <col width="20" customWidth="1" min="7" max="7"/>
-    <col width="20" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" style="25" min="1" max="1"/>
+    <col width="30" customWidth="1" style="25" min="2" max="2"/>
+    <col width="20" customWidth="1" style="25" min="3" max="3"/>
+    <col width="27" customWidth="1" style="25" min="4" max="4"/>
+    <col width="14" customWidth="1" style="25" min="5" max="5"/>
+    <col width="20" customWidth="1" style="25" min="6" max="6"/>
+    <col width="20" customWidth="1" style="25" min="7" max="7"/>
+    <col width="20" customWidth="1" style="25" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="26" t="inlineStr">
         <is>
           <t>年月</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="26" t="inlineStr">
         <is>
           <t>全国港口集装箱吞吐量(万TEU)</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="26" t="inlineStr">
         <is>
           <t>港口吞吐量同比(%)</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="D1" s="26" t="inlineStr">
         <is>
           <t>中国海关出口总额(亿美元)</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="E1" s="26" t="inlineStr">
         <is>
           <t>出口同比(%)</t>
         </is>
       </c>
-      <c r="F1" s="2" t="inlineStr">
+      <c r="F1" s="26" t="inlineStr">
         <is>
           <t>对东盟出口同比(%)</t>
         </is>
       </c>
-      <c r="G1" s="2" t="inlineStr">
+      <c r="G1" s="26" t="inlineStr">
         <is>
           <t>对欧盟出口同比(%)</t>
         </is>
       </c>
-      <c r="H1" s="2" t="inlineStr">
+      <c r="H1" s="26" t="inlineStr">
         <is>
           <t>对美国出口同比(%)</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="25" t="inlineStr">
         <is>
           <t>2025-01</t>
         </is>
       </c>
-      <c r="B2" s="17" t="n">
+      <c r="B2" s="19" t="n">
         <v>2610.5</v>
       </c>
-      <c r="C2" s="17" t="n">
+      <c r="C2" s="19" t="n">
         <v>0.081</v>
       </c>
-      <c r="D2" s="18" t="n">
+      <c r="D2" s="38" t="n">
         <v>2640</v>
       </c>
-      <c r="E2" s="19" t="n">
+      <c r="E2" s="39" t="n">
         <v>0.07099999999999999</v>
       </c>
-      <c r="F2" s="19" t="n">
+      <c r="F2" s="39" t="n">
         <v>0.115</v>
       </c>
-      <c r="G2" s="19" t="n">
+      <c r="G2" s="39" t="n">
         <v>0.021</v>
       </c>
-      <c r="H2" s="19" t="n">
+      <c r="H2" s="39" t="n">
         <v>0.05</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="A3" s="27" t="inlineStr">
         <is>
           <t>2025-02</t>
         </is>
       </c>
-      <c r="B3" s="15" t="n">
+      <c r="B3" s="22" t="n">
         <v>2610.5</v>
       </c>
-      <c r="C3" s="15" t="n">
+      <c r="C3" s="22" t="n">
         <v>0.081</v>
       </c>
-      <c r="D3" s="6" t="n">
+      <c r="D3" s="29" t="n">
         <v>2640</v>
       </c>
-      <c r="E3" s="5" t="n">
+      <c r="E3" s="28" t="n">
         <v>0.07099999999999999</v>
       </c>
-      <c r="F3" s="5" t="n">
+      <c r="F3" s="28" t="n">
         <v>0.115</v>
       </c>
-      <c r="G3" s="5" t="n">
+      <c r="G3" s="28" t="n">
         <v>0.021</v>
       </c>
-      <c r="H3" s="5" t="n">
+      <c r="H3" s="28" t="n">
         <v>0.05</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="9" t="inlineStr">
+      <c r="A4" s="32" t="inlineStr">
         <is>
           <t>2025-03</t>
         </is>
       </c>
-      <c r="B4" s="16" t="n">
+      <c r="B4" s="23" t="n">
         <v>2752</v>
       </c>
-      <c r="C4" s="16" t="n">
+      <c r="C4" s="23" t="n">
         <v>0.065</v>
       </c>
-      <c r="D4" s="12" t="n">
+      <c r="D4" s="34" t="n">
         <v>3080</v>
       </c>
-      <c r="E4" s="11" t="n">
+      <c r="E4" s="33" t="n">
         <v>0.058</v>
       </c>
-      <c r="F4" s="11" t="n">
+      <c r="F4" s="33" t="n">
         <v>0.092</v>
       </c>
-      <c r="G4" s="11" t="n">
+      <c r="G4" s="33" t="n">
         <v>0.034</v>
       </c>
-      <c r="H4" s="11" t="n">
+      <c r="H4" s="33" t="n">
         <v>0.028</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="inlineStr">
+      <c r="A5" s="27" t="inlineStr">
         <is>
           <t>2025-04</t>
         </is>
       </c>
-      <c r="B5" s="15" t="n">
+      <c r="B5" s="22" t="n">
         <v>2780</v>
       </c>
-      <c r="C5" s="15" t="n">
+      <c r="C5" s="22" t="n">
         <v>0.07199999999999999</v>
       </c>
-      <c r="D5" s="6" t="n">
+      <c r="D5" s="29" t="n">
         <v>2985</v>
       </c>
-      <c r="E5" s="5" t="n">
+      <c r="E5" s="28" t="n">
         <v>0.015</v>
       </c>
-      <c r="F5" s="5" t="n">
+      <c r="F5" s="28" t="n">
         <v>0.081</v>
       </c>
-      <c r="G5" s="5" t="n">
+      <c r="G5" s="28" t="n">
         <v>-0.008</v>
       </c>
-      <c r="H5" s="5" t="n">
+      <c r="H5" s="28" t="n">
         <v>-0.142</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="9" t="inlineStr">
+      <c r="A6" s="32" t="inlineStr">
         <is>
           <t>2025-05</t>
         </is>
       </c>
-      <c r="B6" s="16" t="n">
+      <c r="B6" s="23" t="n">
         <v>2935</v>
       </c>
-      <c r="C6" s="16" t="n">
+      <c r="C6" s="23" t="n">
         <v>0.082</v>
       </c>
-      <c r="D6" s="12" t="n">
+      <c r="D6" s="34" t="n">
         <v>3025</v>
       </c>
-      <c r="E6" s="11" t="n">
+      <c r="E6" s="33" t="n">
         <v>0.076</v>
       </c>
-      <c r="F6" s="11" t="n">
+      <c r="F6" s="33" t="n">
         <v>0.124</v>
       </c>
-      <c r="G6" s="11" t="n">
+      <c r="G6" s="33" t="n">
         <v>0.062</v>
       </c>
-      <c r="H6" s="11" t="n">
+      <c r="H6" s="33" t="n">
         <v>-0.035</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="inlineStr">
+      <c r="A7" s="27" t="inlineStr">
         <is>
           <t>2025-06</t>
         </is>
       </c>
-      <c r="B7" s="15" t="n">
+      <c r="B7" s="22" t="n">
         <v>2981</v>
       </c>
-      <c r="C7" s="15" t="n">
+      <c r="C7" s="22" t="n">
         <v>0.075</v>
       </c>
-      <c r="D7" s="6" t="n">
+      <c r="D7" s="29" t="n">
         <v>3070</v>
       </c>
-      <c r="E7" s="5" t="n">
+      <c r="E7" s="28" t="n">
         <v>0.08599999999999999</v>
       </c>
-      <c r="F7" s="5" t="n">
+      <c r="F7" s="28" t="n">
         <v>0.15</v>
       </c>
-      <c r="G7" s="5" t="n">
+      <c r="G7" s="28" t="n">
         <v>0.081</v>
       </c>
-      <c r="H7" s="5" t="n">
+      <c r="H7" s="28" t="n">
         <v>0.012</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="9" t="inlineStr">
+      <c r="A8" s="32" t="inlineStr">
         <is>
           <t>2025-07</t>
         </is>
       </c>
-      <c r="B8" s="16" t="n">
+      <c r="B8" s="23" t="n">
         <v>2975</v>
       </c>
-      <c r="C8" s="16" t="n">
+      <c r="C8" s="23" t="n">
         <v>0.066</v>
       </c>
-      <c r="D8" s="12" t="n">
+      <c r="D8" s="34" t="n">
         <v>3010</v>
       </c>
-      <c r="E8" s="11" t="n">
+      <c r="E8" s="33" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="F8" s="11" t="n">
+      <c r="F8" s="33" t="n">
         <v>0.122</v>
       </c>
-      <c r="G8" s="11" t="n">
+      <c r="G8" s="33" t="n">
         <v>0.055</v>
       </c>
-      <c r="H8" s="11" t="n">
+      <c r="H8" s="33" t="n">
         <v>-0.021</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="inlineStr">
+      <c r="A9" s="27" t="inlineStr">
         <is>
           <t>2025-08</t>
         </is>
       </c>
-      <c r="B9" s="15" t="n">
+      <c r="B9" s="22" t="n">
         <v>2988</v>
       </c>
-      <c r="C9" s="15" t="n">
+      <c r="C9" s="22" t="n">
         <v>0.064</v>
       </c>
-      <c r="D9" s="6" t="n">
+      <c r="D9" s="29" t="n">
         <v>3085</v>
       </c>
-      <c r="E9" s="5" t="n">
+      <c r="E9" s="28" t="n">
         <v>0.08699999999999999</v>
       </c>
-      <c r="F9" s="5" t="n">
+      <c r="F9" s="28" t="n">
         <v>0.158</v>
       </c>
-      <c r="G9" s="5" t="n">
+      <c r="G9" s="28" t="n">
         <v>0.07199999999999999</v>
       </c>
-      <c r="H9" s="5" t="n">
+      <c r="H9" s="28" t="n">
         <v>0.049</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="9" t="inlineStr">
+      <c r="A10" s="32" t="inlineStr">
         <is>
           <t>2025-09</t>
         </is>
       </c>
-      <c r="B10" s="16" t="n">
+      <c r="B10" s="23" t="n">
         <v>2960</v>
       </c>
-      <c r="C10" s="16" t="n">
+      <c r="C10" s="23" t="n">
         <v>0.061</v>
       </c>
-      <c r="D10" s="12" t="n">
+      <c r="D10" s="34" t="n">
         <v>3030</v>
       </c>
-      <c r="E10" s="11" t="n">
+      <c r="E10" s="33" t="n">
         <v>0.024</v>
       </c>
-      <c r="F10" s="11" t="n">
+      <c r="F10" s="33" t="n">
         <v>0.055</v>
       </c>
-      <c r="G10" s="11" t="n">
+      <c r="G10" s="33" t="n">
         <v>0.012</v>
       </c>
-      <c r="H10" s="11" t="n">
+      <c r="H10" s="33" t="n">
         <v>-0.051</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="inlineStr">
+      <c r="A11" s="27" t="inlineStr">
         <is>
           <t>2025-10</t>
         </is>
       </c>
-      <c r="B11" s="15" t="n">
+      <c r="B11" s="22" t="n">
         <v>2925</v>
       </c>
-      <c r="C11" s="15" t="n">
+      <c r="C11" s="22" t="n">
         <v>0.06</v>
       </c>
-      <c r="D11" s="6" t="n">
+      <c r="D11" s="29" t="n">
         <v>3090</v>
       </c>
-      <c r="E11" s="5" t="n">
+      <c r="E11" s="28" t="n">
         <v>0.127</v>
       </c>
-      <c r="F11" s="5" t="n">
+      <c r="F11" s="28" t="n">
         <v>0.158</v>
       </c>
-      <c r="G11" s="5" t="n">
+      <c r="G11" s="28" t="n">
         <v>0.112</v>
       </c>
-      <c r="H11" s="5" t="n">
+      <c r="H11" s="28" t="n">
         <v>0.081</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="9" t="inlineStr">
+      <c r="A12" s="32" t="inlineStr">
         <is>
           <t>2025-11</t>
         </is>
       </c>
-      <c r="B12" s="16" t="n">
+      <c r="B12" s="23" t="n">
         <v>2940</v>
       </c>
-      <c r="C12" s="16" t="n">
+      <c r="C12" s="23" t="n">
         <v>0.058</v>
       </c>
-      <c r="D12" s="12" t="n">
+      <c r="D12" s="34" t="n">
         <v>3120</v>
       </c>
-      <c r="E12" s="11" t="n">
+      <c r="E12" s="33" t="n">
         <v>0.067</v>
       </c>
-      <c r="F12" s="11" t="n">
+      <c r="F12" s="33" t="n">
         <v>0.095</v>
       </c>
-      <c r="G12" s="11" t="n">
+      <c r="G12" s="33" t="n">
         <v>0.048</v>
       </c>
-      <c r="H12" s="11" t="n">
+      <c r="H12" s="33" t="n">
         <v>0.022</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="inlineStr">
+      <c r="A13" s="27" t="inlineStr">
         <is>
           <t>2025-12</t>
         </is>
       </c>
-      <c r="B13" s="15" t="n">
+      <c r="B13" s="22" t="n">
         <v>2990</v>
       </c>
-      <c r="C13" s="15" t="n">
+      <c r="C13" s="22" t="n">
         <v>0.062</v>
       </c>
-      <c r="D13" s="6" t="n">
+      <c r="D13" s="29" t="n">
         <v>3200</v>
       </c>
-      <c r="E13" s="5" t="n">
+      <c r="E13" s="28" t="n">
         <v>0.055</v>
       </c>
-      <c r="F13" s="5" t="n">
+      <c r="F13" s="28" t="n">
         <v>0.08799999999999999</v>
       </c>
-      <c r="G13" s="5" t="n">
+      <c r="G13" s="28" t="n">
         <v>0.039</v>
       </c>
-      <c r="H13" s="5" t="n">
+      <c r="H13" s="28" t="n">
         <v>0.015</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="A14" s="27" t="inlineStr">
         <is>
           <t>2026-01</t>
         </is>
       </c>
-      <c r="B14" s="17" t="n">
+      <c r="B14" s="19" t="n">
         <v>2840</v>
       </c>
-      <c r="C14" s="17" t="n">
+      <c r="C14" s="19" t="n">
         <v>0.08799999999999999</v>
       </c>
-      <c r="D14" s="18" t="n">
+      <c r="D14" s="29" t="n">
         <v>3282.9</v>
       </c>
-      <c r="E14" s="19" t="n">
+      <c r="E14" s="28" t="n">
         <v>0.218</v>
       </c>
-      <c r="F14" s="19" t="n">
+      <c r="F14" s="28" t="n">
         <v>0.229</v>
       </c>
-      <c r="G14" s="19" t="n">
+      <c r="G14" s="28" t="n">
         <v>0.185</v>
       </c>
-      <c r="H14" s="19" t="n">
+      <c r="H14" s="28" t="n">
         <v>0.097</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="9" t="inlineStr">
+      <c r="A15" s="27" t="inlineStr">
         <is>
           <t>2026-02</t>
         </is>
       </c>
-      <c r="B15" s="16" t="n">
+      <c r="B15" s="23" t="n">
         <v>2840</v>
       </c>
-      <c r="C15" s="16" t="n">
+      <c r="C15" s="23" t="n">
         <v>0.08799999999999999</v>
       </c>
-      <c r="D15" s="12" t="n">
+      <c r="D15" s="34" t="n">
         <v>3282.9</v>
       </c>
-      <c r="E15" s="11" t="n">
+      <c r="E15" s="28" t="n">
         <v>0.218</v>
       </c>
-      <c r="F15" s="11" t="n">
+      <c r="F15" s="28" t="n">
         <v>0.229</v>
       </c>
-      <c r="G15" s="11" t="n">
+      <c r="G15" s="28" t="n">
         <v>0.185</v>
       </c>
-      <c r="H15" s="11" t="n">
+      <c r="H15" s="28" t="n">
         <v>0.097</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="inlineStr">
+      <c r="A16" s="27" t="inlineStr">
         <is>
           <t>2026-03</t>
         </is>
       </c>
-      <c r="B16" s="15" t="n">
+      <c r="B16" s="22" t="n">
         <v>3284</v>
       </c>
-      <c r="C16" s="15" t="n">
+      <c r="C16" s="22" t="n">
         <v>0.082</v>
       </c>
-      <c r="D16" s="6" t="n">
+      <c r="D16" s="29" t="n">
         <v>3180</v>
       </c>
-      <c r="E16" s="5" t="n">
+      <c r="E16" s="28" t="n">
         <v>0.125</v>
       </c>
-      <c r="F16" s="5" t="n">
+      <c r="F16" s="28" t="n">
         <v>0.142</v>
       </c>
-      <c r="G16" s="5" t="n">
+      <c r="G16" s="28" t="n">
         <v>0.098</v>
       </c>
-      <c r="H16" s="5" t="n">
+      <c r="H16" s="28" t="n">
         <v>0.051</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="9" t="inlineStr">
+      <c r="A17" s="27" t="inlineStr">
         <is>
           <t>2026-04</t>
         </is>
       </c>
-      <c r="B17" s="16" t="n">
+      <c r="B17" s="23" t="n">
         <v>3120</v>
       </c>
-      <c r="C17" s="16" t="n">
+      <c r="C17" s="23" t="n">
         <v>0.078</v>
       </c>
-      <c r="D17" s="12" t="n">
+      <c r="D17" s="34" t="n">
         <v>3210</v>
       </c>
-      <c r="E17" s="11" t="n">
+      <c r="E17" s="28" t="n">
         <v>0.108</v>
       </c>
-      <c r="F17" s="11" t="n">
+      <c r="F17" s="28" t="n">
         <v>0.135</v>
       </c>
-      <c r="G17" s="11" t="n">
+      <c r="G17" s="28" t="n">
         <v>0.082</v>
       </c>
-      <c r="H17" s="11" t="n">
+      <c r="H17" s="28" t="n">
         <v>0.038</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="3" t="inlineStr">
+      <c r="A18" s="27" t="inlineStr">
         <is>
           <t>2026-05</t>
         </is>
       </c>
-      <c r="B18" s="15" t="n">
+      <c r="B18" s="22" t="n">
         <v>3250</v>
       </c>
-      <c r="C18" s="15" t="n">
+      <c r="C18" s="22" t="n">
         <v>0.08500000000000001</v>
       </c>
-      <c r="D18" s="6" t="n">
+      <c r="D18" s="29" t="n">
         <v>3280</v>
       </c>
-      <c r="E18" s="5" t="n">
+      <c r="E18" s="28" t="n">
         <v>0.153</v>
       </c>
-      <c r="F18" s="5" t="n">
+      <c r="F18" s="28" t="n">
         <v>0.182</v>
       </c>
-      <c r="G18" s="5" t="n">
+      <c r="G18" s="28" t="n">
         <v>0.115</v>
       </c>
-      <c r="H18" s="5" t="n">
+      <c r="H18" s="28" t="n">
         <v>0.062</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="9" t="inlineStr">
+      <c r="A19" s="27" t="inlineStr">
         <is>
           <t>2026-06</t>
         </is>
       </c>
-      <c r="B19" s="16" t="n">
+      <c r="B19" s="23" t="n">
         <v>3310</v>
       </c>
-      <c r="C19" s="16" t="n">
+      <c r="C19" s="23" t="n">
         <v>0.082</v>
       </c>
-      <c r="D19" s="12" t="n">
+      <c r="D19" s="34" t="n">
         <v>3320</v>
       </c>
-      <c r="E19" s="11" t="n">
+      <c r="E19" s="28" t="n">
         <v>0.102</v>
       </c>
-      <c r="F19" s="11" t="n">
+      <c r="F19" s="28" t="n">
         <v>0.128</v>
       </c>
-      <c r="G19" s="11" t="n">
+      <c r="G19" s="28" t="n">
         <v>0.079</v>
       </c>
-      <c r="H19" s="11" t="n">
+      <c r="H19" s="28" t="n">
         <v>0.025</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="3" t="inlineStr">
+      <c r="A20" s="27" t="inlineStr">
         <is>
           <t>2026-07</t>
         </is>
       </c>
-      <c r="B20" s="15" t="n">
+      <c r="B20" s="22" t="n">
         <v>3290</v>
       </c>
-      <c r="C20" s="15" t="n">
+      <c r="C20" s="22" t="n">
         <v>0.075</v>
       </c>
-      <c r="D20" s="6" t="n">
+      <c r="D20" s="29" t="n">
         <v>3290</v>
       </c>
-      <c r="E20" s="5" t="n">
+      <c r="E20" s="28" t="n">
         <v>0.08500000000000001</v>
       </c>
-      <c r="F20" s="5" t="n">
+      <c r="F20" s="28" t="n">
         <v>0.11</v>
       </c>
-      <c r="G20" s="5" t="n">
+      <c r="G20" s="28" t="n">
         <v>0.065</v>
       </c>
-      <c r="H20" s="5" t="n">
+      <c r="H20" s="28" t="n">
         <v>0.018</v>
       </c>
     </row>
@@ -2615,236 +2735,236 @@
   <dimension ref="A1:G8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="24" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="68" customWidth="1" min="7" max="7"/>
+    <col width="20" customWidth="1" style="25" min="1" max="1"/>
+    <col width="30" customWidth="1" style="25" min="2" max="2"/>
+    <col width="18" customWidth="1" style="25" min="3" max="3"/>
+    <col width="24" customWidth="1" style="25" min="4" max="4"/>
+    <col width="22" customWidth="1" style="25" min="5" max="5"/>
+    <col width="18" customWidth="1" style="25" min="6" max="6"/>
+    <col width="68" customWidth="1" style="25" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="26" t="inlineStr">
         <is>
           <t>时间节点</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="26" t="inlineStr">
         <is>
           <t>全球集装箱船队总运力(万TEU)</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="26" t="inlineStr">
         <is>
           <t>运力同比增速(%)</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="D1" s="26" t="inlineStr">
         <is>
           <t>手持订单占运力比例(%)</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="E1" s="26" t="inlineStr">
         <is>
           <t>闲置运力规模(万TEU)</t>
         </is>
       </c>
-      <c r="F1" s="2" t="inlineStr">
+      <c r="F1" s="26" t="inlineStr">
         <is>
           <t>闲置运力比例(%)</t>
         </is>
       </c>
-      <c r="G1" s="2" t="inlineStr">
+      <c r="G1" s="26" t="inlineStr">
         <is>
           <t>行业供给动态简评</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="inlineStr">
+      <c r="A2" s="27" t="inlineStr">
         <is>
           <t>2025 Q1</t>
         </is>
       </c>
-      <c r="B2" s="8" t="n">
+      <c r="B2" s="31" t="n">
         <v>2980</v>
       </c>
-      <c r="C2" s="5" t="n">
+      <c r="C2" s="28" t="n">
         <v>0.082</v>
       </c>
-      <c r="D2" s="5" t="n">
+      <c r="D2" s="28" t="n">
         <v>0.245</v>
       </c>
-      <c r="E2" s="15" t="n">
+      <c r="E2" s="22" t="n">
         <v>28.5</v>
       </c>
-      <c r="F2" s="5" t="n">
+      <c r="F2" s="28" t="n">
         <v>0.0095</v>
       </c>
-      <c r="G2" s="8" t="inlineStr">
+      <c r="G2" s="31" t="inlineStr">
         <is>
           <t>红海绕航好望角吸收约8-10%有效运力，闲置率维持在1%以下的极低水平。</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="9" t="inlineStr">
+      <c r="A3" s="32" t="inlineStr">
         <is>
           <t>2025 Q2</t>
         </is>
       </c>
-      <c r="B3" s="14" t="n">
+      <c r="B3" s="36" t="n">
         <v>3030</v>
       </c>
-      <c r="C3" s="11" t="n">
+      <c r="C3" s="33" t="n">
         <v>0.079</v>
       </c>
-      <c r="D3" s="11" t="n">
+      <c r="D3" s="33" t="n">
         <v>0.228</v>
       </c>
-      <c r="E3" s="16" t="n">
+      <c r="E3" s="23" t="n">
         <v>24.2</v>
       </c>
-      <c r="F3" s="11" t="n">
+      <c r="F3" s="33" t="n">
         <v>0.008</v>
       </c>
-      <c r="G3" s="14" t="inlineStr">
+      <c r="G3" s="36" t="inlineStr">
         <is>
           <t>旺季需求强劲，新船集中交付但迅速被远洋绕航消化，运力极度紧张。</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
+      <c r="A4" s="27" t="inlineStr">
         <is>
           <t>2025 Q3</t>
         </is>
       </c>
-      <c r="B4" s="8" t="n">
+      <c r="B4" s="31" t="n">
         <v>3090</v>
       </c>
-      <c r="C4" s="5" t="n">
+      <c r="C4" s="28" t="n">
         <v>0.075</v>
       </c>
-      <c r="D4" s="5" t="n">
+      <c r="D4" s="28" t="n">
         <v>0.215</v>
       </c>
-      <c r="E4" s="15" t="n">
+      <c r="E4" s="22" t="n">
         <v>31</v>
       </c>
-      <c r="F4" s="5" t="n">
+      <c r="F4" s="28" t="n">
         <v>0.01</v>
       </c>
-      <c r="G4" s="8" t="inlineStr">
+      <c r="G4" s="31" t="inlineStr">
         <is>
           <t>新造船交付继续保持高位，闲置率略有回升但整体仍处于低位。</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="9" t="inlineStr">
+      <c r="A5" s="32" t="inlineStr">
         <is>
           <t>2025 Q4</t>
         </is>
       </c>
-      <c r="B5" s="14" t="n">
+      <c r="B5" s="36" t="n">
         <v>3140</v>
       </c>
-      <c r="C5" s="11" t="n">
+      <c r="C5" s="33" t="n">
         <v>0.07099999999999999</v>
       </c>
-      <c r="D5" s="11" t="n">
+      <c r="D5" s="33" t="n">
         <v>0.202</v>
       </c>
-      <c r="E5" s="16" t="n">
+      <c r="E5" s="23" t="n">
         <v>45</v>
       </c>
-      <c r="F5" s="11" t="n">
+      <c r="F5" s="33" t="n">
         <v>0.0143</v>
       </c>
-      <c r="G5" s="14" t="inlineStr">
+      <c r="G5" s="36" t="inlineStr">
         <is>
           <t>淡季船公司进行定期维护与精细化停航，闲置运力小幅上升。</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="inlineStr">
+      <c r="A6" s="27" t="inlineStr">
         <is>
           <t>2026 Q1</t>
         </is>
       </c>
-      <c r="B6" s="8" t="n">
+      <c r="B6" s="31" t="n">
         <v>3210</v>
       </c>
-      <c r="C6" s="5" t="n">
+      <c r="C6" s="28" t="n">
         <v>0.077</v>
       </c>
-      <c r="D6" s="5" t="n">
+      <c r="D6" s="28" t="n">
         <v>0.198</v>
       </c>
-      <c r="E6" s="15" t="n">
+      <c r="E6" s="22" t="n">
         <v>38</v>
       </c>
-      <c r="F6" s="5" t="n">
+      <c r="F6" s="28" t="n">
         <v>0.0118</v>
       </c>
-      <c r="G6" s="8" t="inlineStr">
+      <c r="G6" s="31" t="inlineStr">
         <is>
           <t>春节后船公司调控运力，中东地缘局势升级引发新一轮绕航需求。</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="9" t="inlineStr">
+      <c r="A7" s="32" t="inlineStr">
         <is>
           <t>2026 Q2</t>
         </is>
       </c>
-      <c r="B7" s="14" t="n">
+      <c r="B7" s="36" t="n">
         <v>3280</v>
       </c>
-      <c r="C7" s="11" t="n">
+      <c r="C7" s="33" t="n">
         <v>0.082</v>
       </c>
-      <c r="D7" s="11" t="n">
+      <c r="D7" s="33" t="n">
         <v>0.192</v>
       </c>
-      <c r="E7" s="16" t="n">
+      <c r="E7" s="23" t="n">
         <v>26</v>
       </c>
-      <c r="F7" s="11" t="n">
+      <c r="F7" s="33" t="n">
         <v>0.007900000000000001</v>
       </c>
-      <c r="G7" s="14" t="inlineStr">
+      <c r="G7" s="36" t="inlineStr">
         <is>
           <t>关税窗口期抢装潮与旺季预热，全行业可用运力再次被全数吸纳。</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="inlineStr">
+      <c r="A8" s="27" t="inlineStr">
         <is>
           <t>2026 Q3 (截至7月)</t>
         </is>
       </c>
-      <c r="B8" s="8" t="n">
+      <c r="B8" s="31" t="n">
         <v>3320</v>
       </c>
-      <c r="C8" s="5" t="n">
+      <c r="C8" s="28" t="n">
         <v>0.074</v>
       </c>
-      <c r="D8" s="5" t="n">
+      <c r="D8" s="28" t="n">
         <v>0.188</v>
       </c>
-      <c r="E8" s="15" t="n">
+      <c r="E8" s="22" t="n">
         <v>29.8</v>
       </c>
-      <c r="F8" s="5" t="n">
+      <c r="F8" s="28" t="n">
         <v>0.008999999999999999</v>
       </c>
-      <c r="G8" s="8" t="inlineStr">
+      <c r="G8" s="31" t="inlineStr">
         <is>
           <t>全球船队突破3300万TEU，但闲置率依然保持在1%附近的紧平衡状态。</t>
         </is>
@@ -2864,155 +2984,155 @@
   <dimension ref="A1:D8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="26" customWidth="1" min="2" max="2"/>
-    <col width="26" customWidth="1" min="3" max="3"/>
-    <col width="85" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" style="25" min="1" max="1"/>
+    <col width="26" customWidth="1" style="25" min="2" max="2"/>
+    <col width="26" customWidth="1" style="25" min="3" max="3"/>
+    <col width="85" customWidth="1" style="25" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="26" t="inlineStr">
         <is>
           <t>时间节点</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="26" t="inlineStr">
         <is>
           <t>美线停航空白航次比例(%)</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="26" t="inlineStr">
         <is>
           <t>欧线停航空白航次比例(%)</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="D1" s="26" t="inlineStr">
         <is>
           <t>海洋联盟运力调控策略</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="inlineStr">
+      <c r="A2" s="27" t="inlineStr">
         <is>
           <t>2025 Q1</t>
         </is>
       </c>
-      <c r="B2" s="5" t="n">
+      <c r="B2" s="28" t="n">
         <v>0.08500000000000001</v>
       </c>
-      <c r="C2" s="5" t="n">
+      <c r="C2" s="28" t="n">
         <v>0.062</v>
       </c>
-      <c r="D2" s="8" t="inlineStr">
+      <c r="D2" s="31" t="inlineStr">
         <is>
           <t>推出Day 9 Product，部署390艘船舶（近500万TEU），通过绕航好望角吸收运力。</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="9" t="inlineStr">
+      <c r="A3" s="32" t="inlineStr">
         <is>
           <t>2025 Q2</t>
         </is>
       </c>
-      <c r="B3" s="11" t="n">
+      <c r="B3" s="33" t="n">
         <v>0.052</v>
       </c>
-      <c r="C3" s="11" t="n">
+      <c r="C3" s="33" t="n">
         <v>0.041</v>
       </c>
-      <c r="D3" s="14" t="inlineStr">
+      <c r="D3" s="36" t="inlineStr">
         <is>
           <t>旺季需求旺盛，停航率显著下行，联盟全面提高船舶开航率并部署加班船。</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
+      <c r="A4" s="27" t="inlineStr">
         <is>
           <t>2025 Q3</t>
         </is>
       </c>
-      <c r="B4" s="5" t="n">
+      <c r="B4" s="28" t="n">
         <v>0.078</v>
       </c>
-      <c r="C4" s="5" t="n">
+      <c r="C4" s="28" t="n">
         <v>0.055</v>
       </c>
-      <c r="D4" s="8" t="inlineStr">
+      <c r="D4" s="31" t="inlineStr">
         <is>
           <t>运价回调期进行精细化Blank Sailings，维持航线满载率。</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="9" t="inlineStr">
+      <c r="A5" s="32" t="inlineStr">
         <is>
           <t>2025 Q4</t>
         </is>
       </c>
-      <c r="B5" s="11" t="n">
+      <c r="B5" s="33" t="n">
         <v>0.145</v>
       </c>
-      <c r="C5" s="11" t="n">
+      <c r="C5" s="33" t="n">
         <v>0.112</v>
       </c>
-      <c r="D5" s="14" t="inlineStr">
+      <c r="D5" s="36" t="inlineStr">
         <is>
           <t>关税波速下淡季大幅提高停航比例，美线取消航次率一度达到14%-18%。</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="inlineStr">
+      <c r="A6" s="27" t="inlineStr">
         <is>
           <t>2026 Q1</t>
         </is>
       </c>
-      <c r="B6" s="5" t="n">
+      <c r="B6" s="28" t="n">
         <v>0.122</v>
       </c>
-      <c r="C6" s="5" t="n">
+      <c r="C6" s="28" t="n">
         <v>0.098</v>
       </c>
-      <c r="D6" s="8" t="inlineStr">
+      <c r="D6" s="31" t="inlineStr">
         <is>
           <t>春节前后实施集中停航（取消136航次），节后推出 Day 10 Product（394艘船/530万TEU）。</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="9" t="inlineStr">
+      <c r="A7" s="32" t="inlineStr">
         <is>
           <t>2026 Q2</t>
         </is>
       </c>
-      <c r="B7" s="11" t="n">
+      <c r="B7" s="33" t="n">
         <v>0.061</v>
       </c>
-      <c r="C7" s="11" t="n">
+      <c r="C7" s="33" t="n">
         <v>0.048</v>
       </c>
-      <c r="D7" s="14" t="inlineStr">
+      <c r="D7" s="36" t="inlineStr">
         <is>
           <t>抢装潮引发全线舱位紧缺，海洋联盟停航率降至5%-6%低位，配合GRI涨价。</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="inlineStr">
+      <c r="A8" s="27" t="inlineStr">
         <is>
           <t>2026 Q3 (截至7月)</t>
         </is>
       </c>
-      <c r="B8" s="5" t="n">
+      <c r="B8" s="28" t="n">
         <v>0.068</v>
       </c>
-      <c r="C8" s="5" t="n">
+      <c r="C8" s="28" t="n">
         <v>0.052</v>
       </c>
-      <c r="D8" s="8" t="inlineStr">
+      <c r="D8" s="31" t="inlineStr">
         <is>
           <t>旺季备货强劲，7月下旬恢复GRI推涨，联盟运力保持极高开航率。</t>
         </is>

--- a/cosco-shipping/数据源/中远海控_行业供需与运价数据.xlsx
+++ b/cosco-shipping/数据源/中远海控_行业供需与运价数据.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="620" windowWidth="38400" windowHeight="19760" tabRatio="600" firstSheet="0" activeTab="3" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="620" windowWidth="38400" windowHeight="19760" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="周运价指数(SCFI&amp;CCFI)" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="需求端-港口吞吐量&amp;出口" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="供给端-运力&amp;闲置率" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="供需调控-停航率&amp;联盟" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="周运价指数(SCFI&amp;CCFI)" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="需求端-港口吞吐量&amp;出口" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="供给端-运力&amp;闲置率" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="供需调控-停航率&amp;联盟" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
@@ -22,7 +22,7 @@
     <numFmt numFmtId="164" formatCode="\+0.0%;\-0.0%;0.0%"/>
     <numFmt numFmtId="165" formatCode="\$#,##0"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="5">
     <font>
       <name val="宋体"/>
       <family val="2"/>
@@ -43,13 +43,6 @@
       <charset val="134"/>
       <family val="2"/>
       <sz val="10"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <family val="2"/>
-      <color theme="1"/>
-      <sz val="10"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <name val="宋体"/>
@@ -89,7 +82,7 @@
       <patternFill/>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -128,21 +121,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FFD9D9D9"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFD9D9D9"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFD9D9D9"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFD9D9D9"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
       <top/>
@@ -151,9 +129,9 @@
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="4"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="3"/>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -202,31 +180,13 @@
     <xf numFmtId="9" fontId="2" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="3" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="3" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="3" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="4" fillId="4" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="4" fillId="4" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="4" fillId="4" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="3" fillId="4" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="3" fillId="4" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="3" fillId="4" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="2" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
@@ -246,14 +206,8 @@
     <xf numFmtId="165" fontId="2" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="3" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="4" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="4" fillId="4" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="3" fillId="4" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="3" fillId="4" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -622,20 +576,20 @@
   <dimension ref="A1:L39"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
-    <col width="13" customWidth="1" style="23" min="1" max="1"/>
-    <col width="15" customWidth="1" style="23" min="2" max="2"/>
-    <col width="16" customWidth="1" style="23" min="3" max="3"/>
-    <col width="15" customWidth="1" style="23" min="4" max="4"/>
-    <col width="16" customWidth="1" style="23" min="5" max="5"/>
-    <col width="20" customWidth="1" style="23" min="6" max="6"/>
-    <col width="22" customWidth="1" style="23" min="7" max="7"/>
-    <col width="20" customWidth="1" style="23" min="8" max="9"/>
-    <col width="22" customWidth="1" style="23" min="10" max="10"/>
-    <col width="13" customWidth="1" style="23" min="11" max="11"/>
-    <col width="79" customWidth="1" style="23" min="12" max="12"/>
+    <col width="13" customWidth="1" style="17" min="1" max="1"/>
+    <col width="15" customWidth="1" style="17" min="2" max="2"/>
+    <col width="16" customWidth="1" style="17" min="3" max="3"/>
+    <col width="15" customWidth="1" style="17" min="4" max="4"/>
+    <col width="16" customWidth="1" style="17" min="5" max="5"/>
+    <col width="20" customWidth="1" style="17" min="6" max="6"/>
+    <col width="22" customWidth="1" style="17" min="7" max="7"/>
+    <col width="20" customWidth="1" style="17" min="8" max="9"/>
+    <col width="22" customWidth="1" style="17" min="10" max="10"/>
+    <col width="13" customWidth="1" style="17" min="11" max="11"/>
+    <col width="255.83203125" bestFit="1" customWidth="1" style="17" min="12" max="12"/>
   </cols>
   <sheetData>
-    <row r="1" ht="18" customHeight="1" s="29">
+    <row r="1" ht="18" customHeight="1" s="23">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>日期</t>
@@ -697,7 +651,7 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="16" customHeight="1" s="29">
+    <row r="2" ht="16" customHeight="1" s="23">
       <c r="A2" s="2" t="inlineStr">
         <is>
           <t>2026-01-09</t>
@@ -706,28 +660,28 @@
       <c r="B2" s="3" t="n">
         <v>1647.39</v>
       </c>
-      <c r="C2" s="30" t="n">
+      <c r="C2" s="24" t="n">
         <v>0</v>
       </c>
       <c r="D2" s="3" t="n">
         <v>1197.6</v>
       </c>
-      <c r="E2" s="30" t="n">
+      <c r="E2" s="24" t="n">
         <v>0.024</v>
       </c>
-      <c r="F2" s="31" t="n">
+      <c r="F2" s="25" t="n">
         <v>1719</v>
       </c>
-      <c r="G2" s="31" t="n">
+      <c r="G2" s="25" t="n">
         <v>3232</v>
       </c>
-      <c r="H2" s="31" t="n">
+      <c r="H2" s="25" t="n">
         <v>2218</v>
       </c>
-      <c r="I2" s="31" t="n">
+      <c r="I2" s="25" t="n">
         <v>3128</v>
       </c>
-      <c r="J2" s="31" t="n">
+      <c r="J2" s="25" t="n">
         <v>1981</v>
       </c>
       <c r="K2" s="6" t="n">
@@ -739,7 +693,7 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="16" customHeight="1" s="29">
+    <row r="3" ht="16" customHeight="1" s="23">
       <c r="A3" s="8" t="inlineStr">
         <is>
           <t>2026-01-16</t>
@@ -748,28 +702,28 @@
       <c r="B3" s="9" t="n">
         <v>1574.12</v>
       </c>
-      <c r="C3" s="32" t="n">
+      <c r="C3" s="26" t="n">
         <v>-0.044476414206715</v>
       </c>
       <c r="D3" s="9" t="n">
         <v>1188.42</v>
       </c>
-      <c r="E3" s="32" t="n">
+      <c r="E3" s="26" t="n">
         <v>-0.00766533066132247</v>
       </c>
-      <c r="F3" s="33" t="n">
+      <c r="F3" s="27" t="n">
         <v>1676</v>
       </c>
-      <c r="G3" s="33" t="n">
+      <c r="G3" s="27" t="n">
         <v>2983</v>
       </c>
-      <c r="H3" s="33" t="n">
+      <c r="H3" s="27" t="n">
         <v>2194</v>
       </c>
-      <c r="I3" s="33" t="n">
+      <c r="I3" s="27" t="n">
         <v>3165</v>
       </c>
-      <c r="J3" s="33" t="n">
+      <c r="J3" s="27" t="n">
         <v>1694</v>
       </c>
       <c r="K3" s="12" t="inlineStr">
@@ -783,7 +737,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="16" customHeight="1" s="29">
+    <row r="4" ht="16" customHeight="1" s="23">
       <c r="A4" s="2" t="inlineStr">
         <is>
           <t>2026-01-23</t>
@@ -792,28 +746,28 @@
       <c r="B4" s="3" t="n">
         <v>1457.86</v>
       </c>
-      <c r="C4" s="30" t="n">
+      <c r="C4" s="24" t="n">
         <v>-0.0738571392269967</v>
       </c>
       <c r="D4" s="3" t="n">
         <v>1175.59</v>
       </c>
-      <c r="E4" s="30" t="n">
+      <c r="E4" s="24" t="n">
         <v>-0.0107958465862239</v>
       </c>
-      <c r="F4" s="31" t="n">
+      <c r="F4" s="25" t="n">
         <v>1595</v>
       </c>
-      <c r="G4" s="31" t="n">
+      <c r="G4" s="25" t="n">
         <v>2756</v>
       </c>
-      <c r="H4" s="31" t="n">
+      <c r="H4" s="25" t="n">
         <v>2084</v>
       </c>
-      <c r="I4" s="31" t="n">
+      <c r="I4" s="25" t="n">
         <v>2896</v>
       </c>
-      <c r="J4" s="31" t="n">
+      <c r="J4" s="25" t="n">
         <v>1288</v>
       </c>
       <c r="K4" s="6" t="n">
@@ -825,7 +779,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="16" customHeight="1" s="29">
+    <row r="5" ht="16" customHeight="1" s="23">
       <c r="A5" s="8" t="inlineStr">
         <is>
           <t>2026-01-30</t>
@@ -834,28 +788,28 @@
       <c r="B5" s="9" t="n">
         <v>1316.75</v>
       </c>
-      <c r="C5" s="32" t="n">
+      <c r="C5" s="26" t="n">
         <v>-0.0967925589562784</v>
       </c>
       <c r="D5" s="9" t="n">
         <v>1152.3</v>
       </c>
-      <c r="E5" s="32" t="n">
+      <c r="E5" s="26" t="n">
         <v>-0.0198113287795915</v>
       </c>
-      <c r="F5" s="33" t="n">
+      <c r="F5" s="27" t="n">
         <v>1418</v>
       </c>
-      <c r="G5" s="33" t="n">
+      <c r="G5" s="27" t="n">
         <v>2424</v>
       </c>
-      <c r="H5" s="33" t="n">
+      <c r="H5" s="27" t="n">
         <v>1867</v>
       </c>
-      <c r="I5" s="33" t="n">
+      <c r="I5" s="27" t="n">
         <v>2605</v>
       </c>
-      <c r="J5" s="33" t="n">
+      <c r="J5" s="27" t="n">
         <v>997</v>
       </c>
       <c r="K5" s="12" t="inlineStr">
@@ -869,7 +823,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="16" customHeight="1" s="29">
+    <row r="6" ht="16" customHeight="1" s="23">
       <c r="A6" s="2" t="inlineStr">
         <is>
           <t>2026-02-06</t>
@@ -878,28 +832,28 @@
       <c r="B6" s="3" t="n">
         <v>1266.56</v>
       </c>
-      <c r="C6" s="30" t="n">
+      <c r="C6" s="24" t="n">
         <v>-0.0381165749003228</v>
       </c>
       <c r="D6" s="3" t="n">
         <v>1095.12</v>
       </c>
-      <c r="E6" s="30" t="n">
+      <c r="E6" s="24" t="n">
         <v>-0.0496224941421506</v>
       </c>
-      <c r="F6" s="31" t="n">
+      <c r="F6" s="25" t="n">
         <v>1403</v>
       </c>
-      <c r="G6" s="31" t="n">
+      <c r="G6" s="25" t="n">
         <v>2291</v>
       </c>
-      <c r="H6" s="31" t="n">
+      <c r="H6" s="25" t="n">
         <v>1801</v>
       </c>
-      <c r="I6" s="31" t="n">
+      <c r="I6" s="25" t="n">
         <v>2530</v>
       </c>
-      <c r="J6" s="31" t="n">
+      <c r="J6" s="25" t="n">
         <v>917</v>
       </c>
       <c r="K6" s="14" t="inlineStr">
@@ -913,7 +867,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="16" customHeight="1" s="29">
+    <row r="7" ht="16" customHeight="1" s="23">
       <c r="A7" s="8" t="inlineStr">
         <is>
           <t>2026-02-13</t>
@@ -922,28 +876,28 @@
       <c r="B7" s="9" t="n">
         <v>1251.46</v>
       </c>
-      <c r="C7" s="32" t="n">
+      <c r="C7" s="26" t="n">
         <v>-0.0119220565942394</v>
       </c>
       <c r="D7" s="9" t="n">
         <v>1068.3</v>
       </c>
-      <c r="E7" s="32" t="n">
+      <c r="E7" s="26" t="n">
         <v>-0.024490466798159</v>
       </c>
-      <c r="F7" s="33" t="n">
+      <c r="F7" s="27" t="n">
         <v>1361</v>
       </c>
-      <c r="G7" s="33" t="n">
+      <c r="G7" s="27" t="n">
         <v>2177</v>
       </c>
-      <c r="H7" s="33" t="n">
+      <c r="H7" s="27" t="n">
         <v>1787</v>
       </c>
-      <c r="I7" s="33" t="n">
+      <c r="I7" s="27" t="n">
         <v>2524</v>
       </c>
-      <c r="J7" s="33" t="n">
+      <c r="J7" s="27" t="n">
         <v>980</v>
       </c>
       <c r="K7" s="15" t="n">
@@ -955,7 +909,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="16" customHeight="1" s="29">
+    <row r="8" ht="16" customHeight="1" s="23">
       <c r="A8" s="2" t="inlineStr">
         <is>
           <t>2026-02-27</t>
@@ -964,28 +918,28 @@
       <c r="B8" s="3" t="n">
         <v>1333.11</v>
       </c>
-      <c r="C8" s="30" t="n">
+      <c r="C8" s="24" t="n">
         <v>0.0652437952471512</v>
       </c>
       <c r="D8" s="3" t="n">
         <v>1044.57</v>
       </c>
-      <c r="E8" s="30" t="n">
+      <c r="E8" s="24" t="n">
         <v>-0.0222128615557428</v>
       </c>
-      <c r="F8" s="31" t="n">
+      <c r="F8" s="25" t="n">
         <v>1420</v>
       </c>
-      <c r="G8" s="31" t="n">
+      <c r="G8" s="25" t="n">
         <v>2305</v>
       </c>
-      <c r="H8" s="31" t="n">
+      <c r="H8" s="25" t="n">
         <v>1857</v>
       </c>
-      <c r="I8" s="31" t="n">
+      <c r="I8" s="25" t="n">
         <v>2691</v>
       </c>
-      <c r="J8" s="31" t="n">
+      <c r="J8" s="25" t="n">
         <v>1327</v>
       </c>
       <c r="K8" s="6" t="n">
@@ -997,7 +951,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="16" customHeight="1" s="29">
+    <row r="9" ht="16" customHeight="1" s="23">
       <c r="A9" s="8" t="inlineStr">
         <is>
           <t>2026-03-06</t>
@@ -1006,28 +960,28 @@
       <c r="B9" s="9" t="n">
         <v>1489.19</v>
       </c>
-      <c r="C9" s="32" t="n">
+      <c r="C9" s="26" t="n">
         <v>0.117079610834815</v>
       </c>
       <c r="D9" s="9" t="n">
         <v>1054.26</v>
       </c>
-      <c r="E9" s="32" t="n">
+      <c r="E9" s="26" t="n">
         <v>0.009276544415405491</v>
       </c>
-      <c r="F9" s="33" t="n">
+      <c r="F9" s="27" t="n">
         <v>1452</v>
       </c>
-      <c r="G9" s="33" t="n">
+      <c r="G9" s="27" t="n">
         <v>2360</v>
       </c>
-      <c r="H9" s="33" t="n">
+      <c r="H9" s="27" t="n">
         <v>1940</v>
       </c>
-      <c r="I9" s="33" t="n">
+      <c r="I9" s="27" t="n">
         <v>2717</v>
       </c>
-      <c r="J9" s="33" t="n">
+      <c r="J9" s="27" t="n">
         <v>2287</v>
       </c>
       <c r="K9" s="12" t="inlineStr">
@@ -1041,7 +995,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="16" customHeight="1" s="29">
+    <row r="10" ht="16" customHeight="1" s="23">
       <c r="A10" s="2" t="inlineStr">
         <is>
           <t>2026-03-13</t>
@@ -1050,28 +1004,28 @@
       <c r="B10" s="3" t="n">
         <v>1710.35</v>
       </c>
-      <c r="C10" s="30" t="n">
+      <c r="C10" s="24" t="n">
         <v>0.148510263969003</v>
       </c>
       <c r="D10" s="3" t="n">
         <v>1072.15</v>
       </c>
-      <c r="E10" s="30" t="n">
+      <c r="E10" s="24" t="n">
         <v>0.0169692485724584</v>
       </c>
-      <c r="F10" s="31" t="n">
+      <c r="F10" s="25" t="n">
         <v>1618</v>
       </c>
-      <c r="G10" s="31" t="n">
+      <c r="G10" s="25" t="n">
         <v>2666</v>
       </c>
-      <c r="H10" s="31" t="n">
+      <c r="H10" s="25" t="n">
         <v>2249</v>
       </c>
-      <c r="I10" s="31" t="n">
+      <c r="I10" s="25" t="n">
         <v>3111</v>
       </c>
-      <c r="J10" s="31" t="n">
+      <c r="J10" s="25" t="n">
         <v>3220</v>
       </c>
       <c r="K10" s="14" t="inlineStr">
@@ -1085,7 +1039,7 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="16" customHeight="1" s="29">
+    <row r="11" ht="16" customHeight="1" s="23">
       <c r="A11" s="8" t="inlineStr">
         <is>
           <t>2026-03-20</t>
@@ -1094,28 +1048,28 @@
       <c r="B11" s="9" t="n">
         <v>1706.95</v>
       </c>
-      <c r="C11" s="32" t="n">
+      <c r="C11" s="26" t="n">
         <v>-0.00198789721402048</v>
       </c>
       <c r="D11" s="9" t="n">
         <v>1110.82</v>
       </c>
-      <c r="E11" s="32" t="n">
+      <c r="E11" s="26" t="n">
         <v>0.0360677144056334</v>
       </c>
-      <c r="F11" s="33" t="n">
+      <c r="F11" s="27" t="n">
         <v>1636</v>
       </c>
-      <c r="G11" s="33" t="n">
+      <c r="G11" s="27" t="n">
         <v>2784</v>
       </c>
-      <c r="H11" s="33" t="n">
+      <c r="H11" s="27" t="n">
         <v>2054</v>
       </c>
-      <c r="I11" s="33" t="n">
+      <c r="I11" s="27" t="n">
         <v>2922</v>
       </c>
-      <c r="J11" s="33" t="n">
+      <c r="J11" s="27" t="n">
         <v>3324</v>
       </c>
       <c r="K11" s="12" t="inlineStr">
@@ -1129,7 +1083,7 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="16" customHeight="1" s="29">
+    <row r="12" ht="16" customHeight="1" s="23">
       <c r="A12" s="2" t="inlineStr">
         <is>
           <t>2026-03-27</t>
@@ -1138,28 +1092,28 @@
       <c r="B12" s="3" t="n">
         <v>1826.77</v>
       </c>
-      <c r="C12" s="30" t="n">
+      <c r="C12" s="24" t="n">
         <v>0.0701953777204956</v>
       </c>
       <c r="D12" s="3" t="n">
         <v>1139.04</v>
       </c>
-      <c r="E12" s="30" t="n">
+      <c r="E12" s="24" t="n">
         <v>0.0254046560198773</v>
       </c>
-      <c r="F12" s="31" t="n">
+      <c r="F12" s="25" t="n">
         <v>1703</v>
       </c>
-      <c r="G12" s="31" t="n">
+      <c r="G12" s="25" t="n">
         <v>2764</v>
       </c>
-      <c r="H12" s="31" t="n">
+      <c r="H12" s="25" t="n">
         <v>2352</v>
       </c>
-      <c r="I12" s="31" t="n">
+      <c r="I12" s="25" t="n">
         <v>3264</v>
       </c>
-      <c r="J12" s="31" t="n">
+      <c r="J12" s="25" t="n">
         <v>3728</v>
       </c>
       <c r="K12" s="14" t="inlineStr">
@@ -1173,7 +1127,7 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="16" customHeight="1" s="29">
+    <row r="13" ht="16" customHeight="1" s="23">
       <c r="A13" s="8" t="inlineStr">
         <is>
           <t>2026-04-03</t>
@@ -1182,28 +1136,28 @@
       <c r="B13" s="9" t="n">
         <v>1854.96</v>
       </c>
-      <c r="C13" s="32" t="n">
+      <c r="C13" s="26" t="n">
         <v>0.0154316087958528</v>
       </c>
       <c r="D13" s="9" t="n">
         <v>1182.45</v>
       </c>
-      <c r="E13" s="32" t="n">
+      <c r="E13" s="26" t="n">
         <v>0.0381110408765277</v>
       </c>
-      <c r="F13" s="33" t="n">
+      <c r="F13" s="27" t="n">
         <v>1650</v>
       </c>
-      <c r="G13" s="33" t="n">
+      <c r="G13" s="27" t="n">
         <v>2684</v>
       </c>
-      <c r="H13" s="33" t="n">
+      <c r="H13" s="27" t="n">
         <v>2359</v>
       </c>
-      <c r="I13" s="33" t="n">
+      <c r="I13" s="27" t="n">
         <v>3354</v>
       </c>
-      <c r="J13" s="33" t="n">
+      <c r="J13" s="27" t="n">
         <v>3977</v>
       </c>
       <c r="K13" s="12" t="inlineStr">
@@ -1217,7 +1171,7 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="16" customHeight="1" s="29">
+    <row r="14" ht="16" customHeight="1" s="23">
       <c r="A14" s="2" t="inlineStr">
         <is>
           <t>2026-04-10</t>
@@ -1226,28 +1180,28 @@
       <c r="B14" s="3" t="n">
         <v>1890.77</v>
       </c>
-      <c r="C14" s="30" t="n">
+      <c r="C14" s="24" t="n">
         <v>0.0193049984905334</v>
       </c>
       <c r="D14" s="3" t="n">
         <v>1201.3</v>
       </c>
-      <c r="E14" s="30" t="n">
+      <c r="E14" s="24" t="n">
         <v>0.0159414774409066</v>
       </c>
-      <c r="F14" s="31" t="n">
+      <c r="F14" s="25" t="n">
         <v>1547</v>
       </c>
-      <c r="G14" s="31" t="n">
+      <c r="G14" s="25" t="n">
         <v>2590</v>
       </c>
-      <c r="H14" s="31" t="n">
+      <c r="H14" s="25" t="n">
         <v>2552</v>
       </c>
-      <c r="I14" s="31" t="n">
+      <c r="I14" s="25" t="n">
         <v>3518</v>
       </c>
-      <c r="J14" s="31" t="n">
+      <c r="J14" s="25" t="n">
         <v>4167</v>
       </c>
       <c r="K14" s="14" t="inlineStr">
@@ -1261,7 +1215,7 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="16" customHeight="1" s="29">
+    <row r="15" ht="16" customHeight="1" s="23">
       <c r="A15" s="8" t="inlineStr">
         <is>
           <t>2026-04-17</t>
@@ -1270,28 +1224,28 @@
       <c r="B15" s="9" t="n">
         <v>1886.54</v>
       </c>
-      <c r="C15" s="32" t="n">
+      <c r="C15" s="26" t="n">
         <v>-0.00223718379284632</v>
       </c>
       <c r="D15" s="9" t="n">
         <v>1220.18</v>
       </c>
-      <c r="E15" s="32" t="n">
+      <c r="E15" s="26" t="n">
         <v>0.0157163073337219</v>
       </c>
-      <c r="F15" s="33" t="n">
+      <c r="F15" s="27" t="n">
         <v>1501</v>
       </c>
-      <c r="G15" s="33" t="n">
+      <c r="G15" s="27" t="n">
         <v>2491</v>
       </c>
-      <c r="H15" s="33" t="n">
+      <c r="H15" s="27" t="n">
         <v>2612</v>
       </c>
-      <c r="I15" s="33" t="n">
+      <c r="I15" s="27" t="n">
         <v>3584</v>
       </c>
-      <c r="J15" s="33" t="n">
+      <c r="J15" s="27" t="n">
         <v>4031</v>
       </c>
       <c r="K15" s="12" t="inlineStr">
@@ -1305,7 +1259,7 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="16" customHeight="1" s="29">
+    <row r="16" ht="16" customHeight="1" s="23">
       <c r="A16" s="2" t="inlineStr">
         <is>
           <t>2026-04-24</t>
@@ -1314,28 +1268,28 @@
       <c r="B16" s="3" t="n">
         <v>1875.26</v>
       </c>
-      <c r="C16" s="30" t="n">
+      <c r="C16" s="24" t="n">
         <v>-0.00597920001696228</v>
       </c>
       <c r="D16" s="3" t="n">
         <v>1233.76</v>
       </c>
-      <c r="E16" s="30" t="n">
+      <c r="E16" s="24" t="n">
         <v>0.0111295054827976</v>
       </c>
-      <c r="F16" s="31" t="n">
+      <c r="F16" s="25" t="n">
         <v>1497</v>
       </c>
-      <c r="G16" s="31" t="n">
+      <c r="G16" s="25" t="n">
         <v>2420</v>
       </c>
-      <c r="H16" s="31" t="n">
+      <c r="H16" s="25" t="n">
         <v>2586</v>
       </c>
-      <c r="I16" s="31" t="n">
+      <c r="I16" s="25" t="n">
         <v>3570</v>
       </c>
-      <c r="J16" s="31" t="n">
+      <c r="J16" s="25" t="n">
         <v>3951</v>
       </c>
       <c r="K16" s="14" t="inlineStr">
@@ -1349,7 +1303,7 @@
         </is>
       </c>
     </row>
-    <row r="17" ht="16" customHeight="1" s="29">
+    <row r="17" ht="16" customHeight="1" s="23">
       <c r="A17" s="8" t="inlineStr">
         <is>
           <t>2026-04-30</t>
@@ -1358,28 +1312,28 @@
       <c r="B17" s="9" t="n">
         <v>1911.4</v>
       </c>
-      <c r="C17" s="32" t="n">
+      <c r="C17" s="26" t="n">
         <v>0.0192719942834594</v>
       </c>
       <c r="D17" s="9" t="n">
         <v>1245.9</v>
       </c>
-      <c r="E17" s="32" t="n">
+      <c r="E17" s="26" t="n">
         <v>0.00983983919076659</v>
       </c>
-      <c r="F17" s="33" t="n">
+      <c r="F17" s="27" t="n">
         <v>1521</v>
       </c>
-      <c r="G17" s="33" t="n">
+      <c r="G17" s="27" t="n">
         <v>2430</v>
       </c>
-      <c r="H17" s="33" t="n">
+      <c r="H17" s="27" t="n">
         <v>2722</v>
       </c>
-      <c r="I17" s="33" t="n">
+      <c r="I17" s="27" t="n">
         <v>3691</v>
       </c>
-      <c r="J17" s="33" t="n">
+      <c r="J17" s="27" t="n">
         <v>3937</v>
       </c>
       <c r="K17" s="12" t="inlineStr">
@@ -1393,7 +1347,7 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="16" customHeight="1" s="29">
+    <row r="18" ht="16" customHeight="1" s="23">
       <c r="A18" s="2" t="inlineStr">
         <is>
           <t>2026-05-08</t>
@@ -1402,28 +1356,28 @@
       <c r="B18" s="3" t="n">
         <v>1954.21</v>
       </c>
-      <c r="C18" s="30" t="n">
+      <c r="C18" s="24" t="n">
         <v>0.022397195772732</v>
       </c>
       <c r="D18" s="3" t="n">
         <v>1278.79</v>
       </c>
-      <c r="E18" s="30" t="n">
+      <c r="E18" s="24" t="n">
         <v>0.0263985873665622</v>
       </c>
-      <c r="F18" s="31" t="n">
+      <c r="F18" s="25" t="n">
         <v>1596</v>
       </c>
-      <c r="G18" s="31" t="n">
+      <c r="G18" s="25" t="n">
         <v>2463</v>
       </c>
-      <c r="H18" s="31" t="n">
+      <c r="H18" s="25" t="n">
         <v>2826</v>
       </c>
-      <c r="I18" s="31" t="n">
+      <c r="I18" s="25" t="n">
         <v>3812</v>
       </c>
-      <c r="J18" s="31" t="n">
+      <c r="J18" s="25" t="n">
         <v>3925</v>
       </c>
       <c r="K18" s="14" t="inlineStr">
@@ -1437,7 +1391,7 @@
         </is>
       </c>
     </row>
-    <row r="19" ht="16" customHeight="1" s="29">
+    <row r="19" ht="16" customHeight="1" s="23">
       <c r="A19" s="8" t="inlineStr">
         <is>
           <t>2026-05-15</t>
@@ -1446,28 +1400,28 @@
       <c r="B19" s="9" t="n">
         <v>2140.66</v>
       </c>
-      <c r="C19" s="32" t="n">
+      <c r="C19" s="26" t="n">
         <v>0.0954093981711279</v>
       </c>
       <c r="D19" s="9" t="n">
         <v>1310.2</v>
       </c>
-      <c r="E19" s="32" t="n">
+      <c r="E19" s="26" t="n">
         <v>0.0245622815317605</v>
       </c>
-      <c r="F19" s="33" t="n">
+      <c r="F19" s="27" t="n">
         <v>1816</v>
       </c>
-      <c r="G19" s="33" t="n">
+      <c r="G19" s="27" t="n">
         <v>3145</v>
       </c>
-      <c r="H19" s="33" t="n">
+      <c r="H19" s="27" t="n">
         <v>3118</v>
       </c>
-      <c r="I19" s="33" t="n">
+      <c r="I19" s="27" t="n">
         <v>4224</v>
       </c>
-      <c r="J19" s="33" t="n">
+      <c r="J19" s="27" t="n">
         <v>4131</v>
       </c>
       <c r="K19" s="15" t="n">
@@ -1479,7 +1433,7 @@
         </is>
       </c>
     </row>
-    <row r="20" ht="16" customHeight="1" s="29">
+    <row r="20" ht="16" customHeight="1" s="23">
       <c r="A20" s="2" t="inlineStr">
         <is>
           <t>2026-05-22</t>
@@ -1488,28 +1442,28 @@
       <c r="B20" s="3" t="n">
         <v>2218.15</v>
       </c>
-      <c r="C20" s="30" t="n">
+      <c r="C20" s="24" t="n">
         <v>0.0361991161604367</v>
       </c>
       <c r="D20" s="3" t="n">
         <v>1332.1</v>
       </c>
-      <c r="E20" s="30" t="n">
+      <c r="E20" s="24" t="n">
         <v>0.0167150053426957</v>
       </c>
-      <c r="F20" s="31" t="n">
+      <c r="F20" s="25" t="n">
         <v>1905</v>
       </c>
-      <c r="G20" s="31" t="n">
+      <c r="G20" s="25" t="n">
         <v>3207</v>
       </c>
-      <c r="H20" s="31" t="n">
+      <c r="H20" s="25" t="n">
         <v>3154</v>
       </c>
-      <c r="I20" s="31" t="n">
+      <c r="I20" s="25" t="n">
         <v>4313</v>
       </c>
-      <c r="J20" s="31" t="n">
+      <c r="J20" s="25" t="n">
         <v>4306</v>
       </c>
       <c r="K20" s="14" t="inlineStr">
@@ -1523,7 +1477,7 @@
         </is>
       </c>
     </row>
-    <row r="21" ht="16" customHeight="1" s="29">
+    <row r="21" ht="16" customHeight="1" s="23">
       <c r="A21" s="8" t="inlineStr">
         <is>
           <t>2026-05-29</t>
@@ -1532,28 +1486,28 @@
       <c r="B21" s="9" t="n">
         <v>2571.73</v>
       </c>
-      <c r="C21" s="32" t="n">
+      <c r="C21" s="26" t="n">
         <v>0.159403106192097</v>
       </c>
       <c r="D21" s="9" t="n">
         <v>1366.76</v>
       </c>
-      <c r="E21" s="32" t="n">
+      <c r="E21" s="26" t="n">
         <v>0.0260190676375649</v>
       </c>
-      <c r="F21" s="33" t="n">
+      <c r="F21" s="27" t="n">
         <v>2475</v>
       </c>
-      <c r="G21" s="33" t="n">
+      <c r="G21" s="27" t="n">
         <v>3750</v>
       </c>
-      <c r="H21" s="33" t="n">
+      <c r="H21" s="27" t="n">
         <v>4149</v>
       </c>
-      <c r="I21" s="33" t="n">
+      <c r="I21" s="27" t="n">
         <v>5333</v>
       </c>
-      <c r="J21" s="33" t="n">
+      <c r="J21" s="27" t="n">
         <v>4462</v>
       </c>
       <c r="K21" s="15" t="n">
@@ -1565,7 +1519,7 @@
         </is>
       </c>
     </row>
-    <row r="22" ht="16" customHeight="1" s="29">
+    <row r="22" ht="16" customHeight="1" s="23">
       <c r="A22" s="2" t="inlineStr">
         <is>
           <t>2026-06-05</t>
@@ -1574,28 +1528,28 @@
       <c r="B22" s="3" t="n">
         <v>2726.48</v>
       </c>
-      <c r="C22" s="30" t="n">
+      <c r="C22" s="24" t="n">
         <v>0.0601735018839458</v>
       </c>
       <c r="D22" s="3" t="n">
         <v>1412.3</v>
       </c>
-      <c r="E22" s="30" t="n">
+      <c r="E22" s="24" t="n">
         <v>0.0333196757294623</v>
       </c>
-      <c r="F22" s="31" t="n">
+      <c r="F22" s="25" t="n">
         <v>2605</v>
       </c>
-      <c r="G22" s="31" t="n">
+      <c r="G22" s="25" t="n">
         <v>3832</v>
       </c>
-      <c r="H22" s="31" t="n">
+      <c r="H22" s="25" t="n">
         <v>4552</v>
       </c>
-      <c r="I22" s="31" t="n">
+      <c r="I22" s="25" t="n">
         <v>5741</v>
       </c>
-      <c r="J22" s="31" t="n">
+      <c r="J22" s="25" t="n">
         <v>4615</v>
       </c>
       <c r="K22" s="14" t="inlineStr">
@@ -1609,7 +1563,7 @@
         </is>
       </c>
     </row>
-    <row r="23" ht="16" customHeight="1" s="29">
+    <row r="23" ht="16" customHeight="1" s="23">
       <c r="A23" s="8" t="inlineStr">
         <is>
           <t>2026-06-12</t>
@@ -1618,28 +1572,28 @@
       <c r="B23" s="9" t="n">
         <v>2985.22</v>
       </c>
-      <c r="C23" s="32" t="n">
+      <c r="C23" s="26" t="n">
         <v>0.0948989172852908</v>
       </c>
       <c r="D23" s="9" t="n">
         <v>1480.11</v>
       </c>
-      <c r="E23" s="32" t="n">
+      <c r="E23" s="26" t="n">
         <v>0.0480138780712314</v>
       </c>
-      <c r="F23" s="33" t="n">
+      <c r="F23" s="27" t="n">
         <v>3064</v>
       </c>
-      <c r="G23" s="33" t="n">
+      <c r="G23" s="27" t="n">
         <v>4172</v>
       </c>
-      <c r="H23" s="33" t="n">
+      <c r="H23" s="27" t="n">
         <v>5101</v>
       </c>
-      <c r="I23" s="33" t="n">
+      <c r="I23" s="27" t="n">
         <v>6321</v>
       </c>
-      <c r="J23" s="33" t="n">
+      <c r="J23" s="27" t="n">
         <v>4816</v>
       </c>
       <c r="K23" s="15" t="n">
@@ -1651,7 +1605,7 @@
         </is>
       </c>
     </row>
-    <row r="24" ht="16" customHeight="1" s="29">
+    <row r="24" ht="16" customHeight="1" s="23">
       <c r="A24" s="8" t="inlineStr">
         <is>
           <t>2026-06-26</t>
@@ -1660,28 +1614,28 @@
       <c r="B24" s="9" t="n">
         <v>3239.64</v>
       </c>
-      <c r="C24" s="32" t="n">
+      <c r="C24" s="26" t="n">
         <v>0.085226549467041</v>
       </c>
       <c r="D24" s="9" t="n">
         <v>1710.47</v>
       </c>
-      <c r="E24" s="32" t="n">
+      <c r="E24" s="26" t="n">
         <v>0.155637081027762</v>
       </c>
-      <c r="F24" s="33" t="n">
+      <c r="F24" s="27" t="n">
         <v>3342</v>
       </c>
-      <c r="G24" s="33" t="n">
+      <c r="G24" s="27" t="n">
         <v>4666</v>
       </c>
-      <c r="H24" s="33" t="n">
+      <c r="H24" s="27" t="n">
         <v>6067</v>
       </c>
-      <c r="I24" s="33" t="n">
+      <c r="I24" s="27" t="n">
         <v>7384</v>
       </c>
-      <c r="J24" s="33" t="n">
+      <c r="J24" s="27" t="n">
         <v>4592</v>
       </c>
       <c r="K24" s="12" t="inlineStr">
@@ -1695,7 +1649,7 @@
         </is>
       </c>
     </row>
-    <row r="25" ht="16" customHeight="1" s="29">
+    <row r="25" ht="16" customHeight="1" s="23">
       <c r="A25" s="2" t="inlineStr">
         <is>
           <t>2026-07-03</t>
@@ -1704,28 +1658,28 @@
       <c r="B25" s="3" t="n">
         <v>3326.87</v>
       </c>
-      <c r="C25" s="30" t="n">
+      <c r="C25" s="24" t="n">
         <v>0.0269258312652023</v>
       </c>
       <c r="D25" s="3" t="n">
         <v>1811.5</v>
       </c>
-      <c r="E25" s="30" t="n">
+      <c r="E25" s="24" t="n">
         <v>0.0590656369302005</v>
       </c>
-      <c r="F25" s="31" t="n">
+      <c r="F25" s="25" t="n">
         <v>3418</v>
       </c>
-      <c r="G25" s="31" t="n">
+      <c r="G25" s="25" t="n">
         <v>4717</v>
       </c>
-      <c r="H25" s="31" t="n">
+      <c r="H25" s="25" t="n">
         <v>6630</v>
       </c>
-      <c r="I25" s="31" t="n">
+      <c r="I25" s="25" t="n">
         <v>8296</v>
       </c>
-      <c r="J25" s="31" t="n">
+      <c r="J25" s="25" t="n">
         <v>4392</v>
       </c>
       <c r="K25" s="14" t="inlineStr">
@@ -1739,7 +1693,7 @@
         </is>
       </c>
     </row>
-    <row r="26" ht="16" customHeight="1" s="29">
+    <row r="26" ht="16" customHeight="1" s="23">
       <c r="A26" s="8" t="inlineStr">
         <is>
           <t>2026-07-10</t>
@@ -1748,28 +1702,28 @@
       <c r="B26" s="9" t="n">
         <v>3184.82</v>
       </c>
-      <c r="C26" s="32" t="n">
+      <c r="C26" s="26" t="n">
         <v>-0.0426977910167815</v>
       </c>
       <c r="D26" s="9" t="n">
         <v>1873.15</v>
       </c>
-      <c r="E26" s="32" t="n">
+      <c r="E26" s="26" t="n">
         <v>0.0340325696936241</v>
       </c>
-      <c r="F26" s="33" t="n">
+      <c r="F26" s="27" t="n">
         <v>3332</v>
       </c>
-      <c r="G26" s="33" t="n">
+      <c r="G26" s="27" t="n">
         <v>4561</v>
       </c>
-      <c r="H26" s="33" t="n">
+      <c r="H26" s="27" t="n">
         <v>6219</v>
       </c>
-      <c r="I26" s="33" t="n">
+      <c r="I26" s="27" t="n">
         <v>8134</v>
       </c>
-      <c r="J26" s="33" t="n">
+      <c r="J26" s="27" t="n">
         <v>4199</v>
       </c>
       <c r="K26" s="12" t="inlineStr">
@@ -1783,7 +1737,7 @@
         </is>
       </c>
     </row>
-    <row r="27" ht="16" customHeight="1" s="29">
+    <row r="27" ht="16" customHeight="1" s="23">
       <c r="A27" s="2" t="inlineStr">
         <is>
           <t>2026-07-17</t>
@@ -1792,28 +1746,28 @@
       <c r="B27" s="3" t="n">
         <v>3080.31</v>
       </c>
-      <c r="C27" s="30" t="n">
+      <c r="C27" s="24" t="n">
         <v>-0.0328150413524157</v>
       </c>
       <c r="D27" s="3" t="n">
         <v>1910.67</v>
       </c>
-      <c r="E27" s="30" t="n">
+      <c r="E27" s="24" t="n">
         <v>0.0200304300242906</v>
       </c>
-      <c r="F27" s="31" t="n">
+      <c r="F27" s="25" t="n">
         <v>3215</v>
       </c>
-      <c r="G27" s="31" t="n">
+      <c r="G27" s="25" t="n">
         <v>4475</v>
       </c>
-      <c r="H27" s="31" t="n">
+      <c r="H27" s="25" t="n">
         <v>5721</v>
       </c>
-      <c r="I27" s="31" t="n">
+      <c r="I27" s="25" t="n">
         <v>8172</v>
       </c>
-      <c r="J27" s="31" t="n">
+      <c r="J27" s="25" t="n">
         <v>4266</v>
       </c>
       <c r="K27" s="14" t="inlineStr">
@@ -1827,7 +1781,7 @@
         </is>
       </c>
     </row>
-    <row r="28" ht="16" customHeight="1" s="29">
+    <row r="28" ht="16" customHeight="1" s="23">
       <c r="A28" s="8" t="inlineStr">
         <is>
           <t>2026-07-24</t>
@@ -1836,28 +1790,28 @@
       <c r="B28" s="9" t="n">
         <v>3062.95</v>
       </c>
-      <c r="C28" s="32" t="n">
+      <c r="C28" s="26" t="n">
         <v>-0.00563579639711587</v>
       </c>
       <c r="D28" s="9" t="n">
         <v>1901.27</v>
       </c>
-      <c r="E28" s="32" t="n">
+      <c r="E28" s="26" t="n">
         <v>-0.00491974019584762</v>
       </c>
-      <c r="F28" s="33" t="n">
+      <c r="F28" s="27" t="n">
         <v>3155</v>
       </c>
-      <c r="G28" s="33" t="n">
+      <c r="G28" s="27" t="n">
         <v>4351</v>
       </c>
-      <c r="H28" s="33" t="n">
+      <c r="H28" s="27" t="n">
         <v>5535</v>
       </c>
-      <c r="I28" s="33" t="n">
+      <c r="I28" s="27" t="n">
         <v>8040</v>
       </c>
-      <c r="J28" s="33" t="n">
+      <c r="J28" s="27" t="n">
         <v>4584</v>
       </c>
       <c r="K28" s="12" t="inlineStr">
@@ -1871,7 +1825,7 @@
         </is>
       </c>
     </row>
-    <row r="29" ht="16" customHeight="1" s="29">
+    <row r="29" ht="16" customHeight="1" s="23">
       <c r="A29" s="2" t="inlineStr">
         <is>
           <t>2026-07-31</t>
@@ -1880,28 +1834,28 @@
       <c r="B29" s="3" t="n">
         <v>3205.97</v>
       </c>
-      <c r="C29" s="30" t="n">
+      <c r="C29" s="24" t="n">
         <v>0.0466935470706344</v>
       </c>
       <c r="D29" s="3" t="n">
         <v>1857.04</v>
       </c>
-      <c r="E29" s="30" t="n">
+      <c r="E29" s="24" t="n">
         <v>-0.0232633976236937</v>
       </c>
-      <c r="F29" s="31" t="n">
+      <c r="F29" s="25" t="n">
         <v>3039</v>
       </c>
-      <c r="G29" s="31" t="n">
+      <c r="G29" s="25" t="n">
         <v>4189</v>
       </c>
       <c r="H29" s="16" t="n">
         <v>6229</v>
       </c>
-      <c r="I29" s="31" t="n">
+      <c r="I29" s="25" t="n">
         <v>9054</v>
       </c>
-      <c r="J29" s="31" t="n">
+      <c r="J29" s="25" t="n">
         <v>4894</v>
       </c>
       <c r="K29" s="14" t="inlineStr">
@@ -1915,7 +1869,7 @@
         </is>
       </c>
     </row>
-    <row r="30" ht="16" customHeight="1" s="29">
+    <row r="30" ht="16" customHeight="1" s="23">
       <c r="A30" s="2" t="inlineStr">
         <is>
           <t>2026-08-07</t>
@@ -1924,28 +1878,28 @@
       <c r="B30" s="3" t="n">
         <v>3276.14</v>
       </c>
-      <c r="C30" s="30" t="n">
+      <c r="C30" s="24" t="n">
         <v>0.0218872915217547</v>
       </c>
       <c r="D30" s="3" t="n">
         <v>1839.61</v>
       </c>
-      <c r="E30" s="30" t="n">
+      <c r="E30" s="24" t="n">
         <v>-0.009385904450092689</v>
       </c>
-      <c r="F30" s="31" t="n">
+      <c r="F30" s="25" t="n">
         <v>2964</v>
       </c>
-      <c r="G30" s="31" t="n">
+      <c r="G30" s="25" t="n">
         <v>4048</v>
       </c>
-      <c r="H30" s="31" t="n">
+      <c r="H30" s="25" t="n">
         <v>6484</v>
       </c>
-      <c r="I30" s="31" t="n">
+      <c r="I30" s="25" t="n">
         <v>9290</v>
       </c>
-      <c r="J30" s="31" t="n">
+      <c r="J30" s="25" t="n">
         <v>5258</v>
       </c>
       <c r="K30" s="14" t="inlineStr">
@@ -1959,7 +1913,7 @@
         </is>
       </c>
     </row>
-    <row r="31" ht="16" customHeight="1" s="29">
+    <row r="31" ht="16" customHeight="1" s="23">
       <c r="A31" s="2" t="inlineStr">
         <is>
           <t>2026-08-14</t>
@@ -1968,28 +1922,28 @@
       <c r="B31" s="3" t="n">
         <v>3355.24</v>
       </c>
-      <c r="C31" s="30" t="n">
+      <c r="C31" s="24" t="n">
         <v>0.024</v>
       </c>
       <c r="D31" s="3" t="n">
         <v>1846.96</v>
       </c>
-      <c r="E31" s="30" t="n">
+      <c r="E31" s="24" t="n">
         <v>0.004</v>
       </c>
-      <c r="F31" s="31" t="n">
+      <c r="F31" s="25" t="n">
         <v>2945</v>
       </c>
-      <c r="G31" s="31" t="n">
+      <c r="G31" s="25" t="n">
         <v>3929</v>
       </c>
-      <c r="H31" s="31" t="n">
+      <c r="H31" s="25" t="n">
         <v>6714</v>
       </c>
-      <c r="I31" s="31" t="n">
+      <c r="I31" s="25" t="n">
         <v>9568</v>
       </c>
-      <c r="J31" s="31" t="n">
+      <c r="J31" s="25" t="n">
         <v>5422</v>
       </c>
       <c r="K31" s="14" t="inlineStr">
@@ -2003,7 +1957,7 @@
         </is>
       </c>
     </row>
-    <row r="32" ht="16" customHeight="1" s="29">
+    <row r="32" ht="16" customHeight="1" s="23">
       <c r="A32" s="2" t="inlineStr">
         <is>
           <t>2026-08-21</t>
@@ -2012,28 +1966,28 @@
       <c r="B32" s="3" t="n">
         <v>3409.63</v>
       </c>
-      <c r="C32" s="30" t="n">
+      <c r="C32" s="24" t="n">
         <v>0.016</v>
       </c>
       <c r="D32" s="3" t="n">
         <v>1821.65</v>
       </c>
-      <c r="E32" s="30" t="n">
+      <c r="E32" s="24" t="n">
         <v>-0.014</v>
       </c>
-      <c r="F32" s="31" t="n">
+      <c r="F32" s="25" t="n">
         <v>2842</v>
       </c>
-      <c r="G32" s="31" t="n">
+      <c r="G32" s="25" t="n">
         <v>3767</v>
       </c>
-      <c r="H32" s="31" t="n">
+      <c r="H32" s="25" t="n">
         <v>6765</v>
       </c>
-      <c r="I32" s="31" t="n">
+      <c r="I32" s="25" t="n">
         <v>9700</v>
       </c>
-      <c r="J32" s="31" t="n">
+      <c r="J32" s="25" t="n">
         <v>5729</v>
       </c>
       <c r="K32" s="14" t="inlineStr">
@@ -2047,7 +2001,7 @@
         </is>
       </c>
     </row>
-    <row r="33" ht="16" customHeight="1" s="29">
+    <row r="33" ht="16" customHeight="1" s="23">
       <c r="A33" s="2" t="inlineStr">
         <is>
           <t>2026-08-28</t>
@@ -2056,28 +2010,28 @@
       <c r="B33" s="3" t="n">
         <v>3509.53</v>
       </c>
-      <c r="C33" s="30" t="n">
+      <c r="C33" s="24" t="n">
         <v>0.029</v>
       </c>
       <c r="D33" s="3" t="n">
         <v>1833.99</v>
       </c>
-      <c r="E33" s="30" t="n">
+      <c r="E33" s="24" t="n">
         <v>0.007</v>
       </c>
-      <c r="F33" s="31" t="n">
+      <c r="F33" s="25" t="n">
         <v>2716</v>
       </c>
-      <c r="G33" s="31" t="n">
+      <c r="G33" s="25" t="n">
         <v>3557</v>
       </c>
-      <c r="H33" s="31" t="n">
+      <c r="H33" s="25" t="n">
         <v>6940</v>
       </c>
-      <c r="I33" s="31" t="n">
+      <c r="I33" s="25" t="n">
         <v>10046</v>
       </c>
-      <c r="J33" s="31" t="n">
+      <c r="J33" s="25" t="n">
         <v>6139</v>
       </c>
       <c r="K33" s="14" t="inlineStr">
@@ -2091,7 +2045,7 @@
         </is>
       </c>
     </row>
-    <row r="34" ht="16" customHeight="1" s="29">
+    <row r="34" ht="16" customHeight="1" s="23">
       <c r="A34" s="2" t="inlineStr">
         <is>
           <t>2026-09-04</t>
@@ -2100,28 +2054,28 @@
       <c r="B34" s="3" t="n">
         <v>3590.05</v>
       </c>
-      <c r="C34" s="30" t="n">
+      <c r="C34" s="24" t="n">
         <v>0.023</v>
       </c>
       <c r="D34" s="3" t="n">
         <v>1837.01</v>
       </c>
-      <c r="E34" s="30" t="n">
+      <c r="E34" s="24" t="n">
         <v>0.0016</v>
       </c>
-      <c r="F34" s="31" t="n">
+      <c r="F34" s="25" t="n">
         <v>2643</v>
       </c>
-      <c r="G34" s="31" t="n">
+      <c r="G34" s="25" t="n">
         <v>3442</v>
       </c>
-      <c r="H34" s="31" t="n">
+      <c r="H34" s="25" t="n">
         <v>7242</v>
       </c>
-      <c r="I34" s="31" t="n">
+      <c r="I34" s="25" t="n">
         <v>10324</v>
       </c>
-      <c r="J34" s="31" t="n">
+      <c r="J34" s="25" t="n">
         <v>6135</v>
       </c>
       <c r="K34" s="14" t="inlineStr">
@@ -2135,221 +2089,221 @@
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="17" t="inlineStr">
+    <row r="35" ht="16" customHeight="1" s="23">
+      <c r="A35" s="2" t="inlineStr">
         <is>
           <t>2026-09-11</t>
         </is>
       </c>
-      <c r="B35" s="18" t="n">
+      <c r="B35" s="3" t="n">
         <v>3662.18</v>
       </c>
-      <c r="C35" s="34" t="n">
+      <c r="C35" s="24" t="n">
         <v>0.02</v>
       </c>
-      <c r="D35" s="18" t="n">
+      <c r="D35" s="3" t="n">
         <v>1862.18</v>
       </c>
-      <c r="E35" s="34" t="n">
+      <c r="E35" s="24" t="n">
         <v>0.014</v>
       </c>
-      <c r="F35" s="35" t="n">
+      <c r="F35" s="25" t="n">
         <v>2545</v>
       </c>
-      <c r="G35" s="35" t="n">
+      <c r="G35" s="25" t="n">
         <v>3299</v>
       </c>
-      <c r="H35" s="35" t="n">
+      <c r="H35" s="25" t="n">
         <v>7339</v>
       </c>
-      <c r="I35" s="35" t="n">
+      <c r="I35" s="25" t="n">
         <v>10479</v>
       </c>
-      <c r="J35" s="35" t="n">
+      <c r="J35" s="25" t="n">
         <v>6311</v>
       </c>
-      <c r="K35" s="21" t="inlineStr">
+      <c r="K35" s="14" t="inlineStr">
         <is>
           <t>&gt;95%</t>
         </is>
       </c>
-      <c r="L35" s="22" t="inlineStr">
+      <c r="L35" s="7" t="inlineStr">
         <is>
           <t>SCFI报3662.18(+2.0%)，CCFI报1862.18(+1.4%)。欧洲2545(-3.7%)、地中海3299(-4.2%)回落；美西7339(+1.3%)、美东10479(+1.5%)上涨；波斯湾6311(+2.9%)因中东紧张续涨。</t>
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="17" t="inlineStr">
+    <row r="36" ht="16" customHeight="1" s="23">
+      <c r="A36" s="2" t="inlineStr">
         <is>
           <t>2026-09-18</t>
         </is>
       </c>
-      <c r="B36" s="18" t="n">
+      <c r="B36" s="3" t="n">
         <v>3687.83</v>
       </c>
-      <c r="C36" s="34" t="n">
+      <c r="C36" s="24" t="n">
         <v>0.007</v>
       </c>
-      <c r="D36" s="18" t="n">
+      <c r="D36" s="3" t="n">
         <v>1897.15</v>
       </c>
-      <c r="E36" s="34" t="n">
+      <c r="E36" s="24" t="n">
         <v>0.0188</v>
       </c>
-      <c r="F36" s="35" t="n">
+      <c r="F36" s="25" t="n">
         <v>2425</v>
       </c>
-      <c r="G36" s="35" t="n">
+      <c r="G36" s="25" t="n">
         <v>3125</v>
       </c>
-      <c r="H36" s="35" t="n">
+      <c r="H36" s="25" t="n">
         <v>7560</v>
       </c>
-      <c r="I36" s="35" t="n">
+      <c r="I36" s="25" t="n">
         <v>10579</v>
       </c>
-      <c r="J36" s="35" t="n">
+      <c r="J36" s="25" t="n">
         <v>6246</v>
       </c>
-      <c r="K36" s="21" t="inlineStr">
+      <c r="K36" s="14" t="inlineStr">
         <is>
           <t>&gt;95%</t>
         </is>
       </c>
-      <c r="L36" s="22" t="inlineStr">
+      <c r="L36" s="7" t="inlineStr">
         <is>
           <t>SCFI报3687.83(+0.7%)，CCFI报1897.15(+1.9%)。欧洲2425(-4.7%)、地中海3125(-5.3%)回落；美西7560(+3.0%)、美东10579(+1.0%)上涨；波斯湾6246(-1.0%)因中东紧张续跌；澳新2944(+6.9%)、南美7703(-10.0%)、东南亚5611.26(+13.0%)分化。</t>
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="17" t="inlineStr">
+    <row r="37" ht="16" customHeight="1" s="23">
+      <c r="A37" s="2" t="inlineStr">
         <is>
           <t>2026-09-24</t>
         </is>
       </c>
-      <c r="B37" s="18" t="n">
+      <c r="B37" s="3" t="n">
         <v>3686.62</v>
       </c>
-      <c r="C37" s="34" t="n">
+      <c r="C37" s="24" t="n">
         <v>-0.0003</v>
       </c>
-      <c r="D37" s="18" t="n">
+      <c r="D37" s="3" t="n">
         <v>1917.68</v>
       </c>
-      <c r="E37" s="34" t="n">
+      <c r="E37" s="24" t="n">
         <v>0.0108</v>
       </c>
-      <c r="F37" s="35" t="n">
+      <c r="F37" s="25" t="n">
         <v>2313</v>
       </c>
-      <c r="G37" s="35" t="n">
+      <c r="G37" s="25" t="n">
         <v>3065</v>
       </c>
-      <c r="H37" s="35" t="n">
+      <c r="H37" s="25" t="n">
         <v>7463</v>
       </c>
-      <c r="I37" s="35" t="n">
+      <c r="I37" s="25" t="n">
         <v>10497</v>
       </c>
-      <c r="J37" s="35" t="n">
+      <c r="J37" s="25" t="n">
         <v>6586</v>
       </c>
-      <c r="K37" s="21" t="inlineStr">
+      <c r="K37" s="14" t="inlineStr">
         <is>
           <t>&gt;95%</t>
         </is>
       </c>
-      <c r="L37" s="22" t="inlineStr">
+      <c r="L37" s="7" t="inlineStr">
         <is>
           <t>SCFI报3686.62(-0.03%，较上期-1.21点)，CCFI报1917.68(+1.1%)。欧洲2313(-4.6%)、地中海3065(-1.9%)回落；美西7463(-1.3%)、美东10497(-0.8%)回落；波斯湾6586(+5.4%)因中东紧张续涨；澳新2833(-3.8%)、南美6530(-15.2%)、东南亚5794.79(+3.3%)分化。</t>
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="0" t="inlineStr">
+    <row r="38" ht="16" customHeight="1" s="23">
+      <c r="A38" s="2" t="inlineStr">
         <is>
           <t>2026-09-30</t>
         </is>
       </c>
-      <c r="B38" s="0" t="n">
+      <c r="B38" s="3" t="n">
         <v>3662.3</v>
       </c>
-      <c r="C38" s="0" t="n">
+      <c r="C38" s="24" t="n">
         <v>-0.0066</v>
       </c>
-      <c r="D38" s="0" t="n">
+      <c r="D38" s="3" t="n">
         <v>1923.93</v>
       </c>
-      <c r="E38" s="0" t="n">
+      <c r="E38" s="24" t="n">
         <v>0.0033</v>
       </c>
-      <c r="F38" s="0" t="n">
+      <c r="F38" s="25" t="n">
         <v>2199</v>
       </c>
-      <c r="G38" s="0" t="n">
+      <c r="G38" s="25" t="n">
         <v>2996</v>
       </c>
-      <c r="H38" s="0" t="n">
+      <c r="H38" s="25" t="n">
         <v>7578</v>
       </c>
-      <c r="I38" s="0" t="n">
+      <c r="I38" s="25" t="n">
         <v>10528</v>
       </c>
-      <c r="J38" s="0" t="n">
+      <c r="J38" s="25" t="n">
         <v>6489</v>
       </c>
-      <c r="K38" s="0" t="inlineStr">
+      <c r="K38" s="14" t="inlineStr">
         <is>
           <t>&gt;95%</t>
         </is>
       </c>
-      <c r="L38" s="0" t="inlineStr">
+      <c r="L38" s="7" t="inlineStr">
         <is>
           <t>SCFI报3662.30(-0.7%，较上期-24.32点)，CCFI报1923.93(+0.3%)。节前市场略显平淡，多数航线回落：欧洲2199(-4.9%)、地中海2996(-2.3%)继续回落；美西7578(+1.5%)、美东10528(+0.3%)受中美经贸磋商达成多项共识(含300亿美元对等降税安排)带动节前上涨；波斯湾6489(-1.5%)小幅回落；澳新2762(-2.5%)、南美5980(-8.4%)继续下行；东南亚指数5825.70(+0.5%)逆势上涨。宏观：9月中国综合PMI重返扩张区间升至50.7；欧元区9月综合PMI 53.1为2023年4月以来最高，企业投入与产出价格4个月来最快上涨。</t>
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="0" t="inlineStr">
+    <row r="39" ht="16" customHeight="1" s="23">
+      <c r="A39" s="2" t="inlineStr">
         <is>
           <t>2026-10-09</t>
         </is>
       </c>
-      <c r="B39" s="0" t="n">
+      <c r="B39" s="3" t="n">
         <v>3664.11</v>
       </c>
-      <c r="C39" s="0" t="n">
+      <c r="C39" s="24" t="n">
         <v>0.0005</v>
       </c>
-      <c r="D39" s="0" t="n">
+      <c r="D39" s="3" t="n">
         <v>1912.38</v>
       </c>
-      <c r="E39" s="0" t="n">
+      <c r="E39" s="24" t="n">
         <v>-0.006</v>
       </c>
-      <c r="F39" s="0" t="n">
+      <c r="F39" s="25" t="n">
         <v>2274</v>
       </c>
-      <c r="G39" s="0" t="n">
+      <c r="G39" s="25" t="n">
         <v>3002</v>
       </c>
-      <c r="H39" s="0" t="n">
+      <c r="H39" s="25" t="n">
         <v>7584</v>
       </c>
-      <c r="I39" s="0" t="n">
+      <c r="I39" s="25" t="n">
         <v>10524</v>
       </c>
-      <c r="J39" s="0" t="n">
+      <c r="J39" s="25" t="n">
         <v>6452</v>
       </c>
-      <c r="K39" s="0" t="inlineStr">
+      <c r="K39" s="14" t="inlineStr">
         <is>
           <t>&gt;95%</t>
         </is>
       </c>
-      <c r="L39" s="0" t="inlineStr">
+      <c r="L39" s="7" t="inlineStr">
         <is>
           <t>SCFI报3664.11(持平，较上期+1.81点)，CCFI报1912.38(-0.6%)。国庆长假后市场平稳恢复，多数航线小幅波动：欧洲2274(+3.4%)、地中海3002(+0.2%)小幅上涨；美西7584(+0.1%)、美东10524(持平)高位盘整；波斯湾6452(-0.6%)小幅回落；澳新2762(持平)、南美5925(-0.9%)、东南亚5769.48(-1.0%)。宏观：欧元区9月CPI同比+3.8%创2023年9月以来最高(中东推高能源价格，市场预期欧央行再加息)；美国9月非农仅增2.9万大幅低于预期，失业率升至4.2%，劳动力市场显现放缓迹象。</t>
         </is>
@@ -2369,15 +2323,15 @@
   <dimension ref="A1:H21"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
-    <col width="13" customWidth="1" style="23" min="1" max="1"/>
-    <col width="30" customWidth="1" style="23" min="2" max="2"/>
-    <col width="20" customWidth="1" style="23" min="3" max="3"/>
-    <col width="27" customWidth="1" style="23" min="4" max="4"/>
-    <col width="14" customWidth="1" style="23" min="5" max="5"/>
-    <col width="20" customWidth="1" style="23" min="6" max="8"/>
+    <col width="13" customWidth="1" style="17" min="1" max="1"/>
+    <col width="30" customWidth="1" style="17" min="2" max="2"/>
+    <col width="20" customWidth="1" style="17" min="3" max="3"/>
+    <col width="27" customWidth="1" style="17" min="4" max="4"/>
+    <col width="14" customWidth="1" style="17" min="5" max="5"/>
+    <col width="20" customWidth="1" style="17" min="6" max="8"/>
   </cols>
   <sheetData>
-    <row r="1" ht="18" customHeight="1" s="29">
+    <row r="1" ht="18" customHeight="1" s="23">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>年月</t>
@@ -2420,558 +2374,562 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="23" t="inlineStr">
+      <c r="A2" s="17" t="inlineStr">
         <is>
           <t>2025-01</t>
         </is>
       </c>
-      <c r="B2" s="24" t="n">
+      <c r="B2" s="18" t="n">
         <v>2610.5</v>
       </c>
-      <c r="C2" s="24" t="n">
+      <c r="C2" s="18" t="n">
         <v>0.081</v>
       </c>
-      <c r="D2" s="36" t="n">
+      <c r="D2" s="28" t="n">
         <v>2640</v>
       </c>
-      <c r="E2" s="37" t="n">
+      <c r="E2" s="29" t="n">
         <v>0.07099999999999999</v>
       </c>
-      <c r="F2" s="37" t="n">
+      <c r="F2" s="29" t="n">
         <v>0.115</v>
       </c>
-      <c r="G2" s="37" t="n">
+      <c r="G2" s="29" t="n">
         <v>0.021</v>
       </c>
-      <c r="H2" s="37" t="n">
+      <c r="H2" s="29" t="n">
         <v>0.05</v>
       </c>
     </row>
-    <row r="3" ht="16" customHeight="1" s="29">
+    <row r="3" ht="16" customHeight="1" s="23">
       <c r="A3" s="2" t="inlineStr">
         <is>
           <t>2025-02</t>
         </is>
       </c>
-      <c r="B3" s="27" t="n">
+      <c r="B3" s="21" t="n">
         <v>2610.5</v>
       </c>
-      <c r="C3" s="27" t="n">
+      <c r="C3" s="21" t="n">
         <v>0.081</v>
       </c>
-      <c r="D3" s="31" t="n">
+      <c r="D3" s="25" t="n">
         <v>2640</v>
       </c>
-      <c r="E3" s="30" t="n">
+      <c r="E3" s="24" t="n">
         <v>0.07099999999999999</v>
       </c>
-      <c r="F3" s="30" t="n">
+      <c r="F3" s="24" t="n">
         <v>0.115</v>
       </c>
-      <c r="G3" s="30" t="n">
+      <c r="G3" s="24" t="n">
         <v>0.021</v>
       </c>
-      <c r="H3" s="30" t="n">
+      <c r="H3" s="24" t="n">
         <v>0.05</v>
       </c>
     </row>
-    <row r="4" ht="16" customHeight="1" s="29">
+    <row r="4" ht="16" customHeight="1" s="23">
       <c r="A4" s="8" t="inlineStr">
         <is>
           <t>2025-03</t>
         </is>
       </c>
-      <c r="B4" s="28" t="n">
+      <c r="B4" s="22" t="n">
         <v>2752</v>
       </c>
-      <c r="C4" s="28" t="n">
+      <c r="C4" s="22" t="n">
         <v>0.065</v>
       </c>
-      <c r="D4" s="33" t="n">
+      <c r="D4" s="27" t="n">
         <v>3080</v>
       </c>
-      <c r="E4" s="32" t="n">
+      <c r="E4" s="26" t="n">
         <v>0.058</v>
       </c>
-      <c r="F4" s="32" t="n">
+      <c r="F4" s="26" t="n">
         <v>0.092</v>
       </c>
-      <c r="G4" s="32" t="n">
+      <c r="G4" s="26" t="n">
         <v>0.034</v>
       </c>
-      <c r="H4" s="32" t="n">
+      <c r="H4" s="26" t="n">
         <v>0.028</v>
       </c>
     </row>
-    <row r="5" ht="16" customHeight="1" s="29">
+    <row r="5" ht="16" customHeight="1" s="23">
       <c r="A5" s="2" t="inlineStr">
         <is>
           <t>2025-04</t>
         </is>
       </c>
-      <c r="B5" s="27" t="n">
+      <c r="B5" s="21" t="n">
         <v>2780</v>
       </c>
-      <c r="C5" s="27" t="n">
+      <c r="C5" s="21" t="n">
         <v>0.07199999999999999</v>
       </c>
-      <c r="D5" s="31" t="n">
+      <c r="D5" s="25" t="n">
         <v>2985</v>
       </c>
-      <c r="E5" s="30" t="n">
+      <c r="E5" s="24" t="n">
         <v>0.015</v>
       </c>
-      <c r="F5" s="30" t="n">
+      <c r="F5" s="24" t="n">
         <v>0.081</v>
       </c>
-      <c r="G5" s="30" t="n">
+      <c r="G5" s="24" t="n">
         <v>-0.008</v>
       </c>
-      <c r="H5" s="30" t="n">
+      <c r="H5" s="24" t="n">
         <v>-0.142</v>
       </c>
     </row>
-    <row r="6" ht="16" customHeight="1" s="29">
+    <row r="6" ht="16" customHeight="1" s="23">
       <c r="A6" s="8" t="inlineStr">
         <is>
           <t>2025-05</t>
         </is>
       </c>
-      <c r="B6" s="28" t="n">
+      <c r="B6" s="22" t="n">
         <v>2935</v>
       </c>
-      <c r="C6" s="28" t="n">
+      <c r="C6" s="22" t="n">
         <v>0.082</v>
       </c>
-      <c r="D6" s="33" t="n">
+      <c r="D6" s="27" t="n">
         <v>3025</v>
       </c>
-      <c r="E6" s="32" t="n">
+      <c r="E6" s="26" t="n">
         <v>0.076</v>
       </c>
-      <c r="F6" s="32" t="n">
+      <c r="F6" s="26" t="n">
         <v>0.124</v>
       </c>
-      <c r="G6" s="32" t="n">
+      <c r="G6" s="26" t="n">
         <v>0.062</v>
       </c>
-      <c r="H6" s="32" t="n">
+      <c r="H6" s="26" t="n">
         <v>-0.035</v>
       </c>
     </row>
-    <row r="7" ht="16" customHeight="1" s="29">
+    <row r="7" ht="16" customHeight="1" s="23">
       <c r="A7" s="2" t="inlineStr">
         <is>
           <t>2025-06</t>
         </is>
       </c>
-      <c r="B7" s="27" t="n">
+      <c r="B7" s="21" t="n">
         <v>2981</v>
       </c>
-      <c r="C7" s="27" t="n">
+      <c r="C7" s="21" t="n">
         <v>0.075</v>
       </c>
-      <c r="D7" s="31" t="n">
+      <c r="D7" s="25" t="n">
         <v>3070</v>
       </c>
-      <c r="E7" s="30" t="n">
+      <c r="E7" s="24" t="n">
         <v>0.08599999999999999</v>
       </c>
-      <c r="F7" s="30" t="n">
+      <c r="F7" s="24" t="n">
         <v>0.15</v>
       </c>
-      <c r="G7" s="30" t="n">
+      <c r="G7" s="24" t="n">
         <v>0.081</v>
       </c>
-      <c r="H7" s="30" t="n">
+      <c r="H7" s="24" t="n">
         <v>0.012</v>
       </c>
     </row>
-    <row r="8" ht="16" customHeight="1" s="29">
+    <row r="8" ht="16" customHeight="1" s="23">
       <c r="A8" s="8" t="inlineStr">
         <is>
           <t>2025-07</t>
         </is>
       </c>
-      <c r="B8" s="28" t="n">
+      <c r="B8" s="22" t="n">
         <v>2975</v>
       </c>
-      <c r="C8" s="28" t="n">
+      <c r="C8" s="22" t="n">
         <v>0.066</v>
       </c>
-      <c r="D8" s="33" t="n">
+      <c r="D8" s="27" t="n">
         <v>3010</v>
       </c>
-      <c r="E8" s="32" t="n">
+      <c r="E8" s="26" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="F8" s="32" t="n">
+      <c r="F8" s="26" t="n">
         <v>0.122</v>
       </c>
-      <c r="G8" s="32" t="n">
+      <c r="G8" s="26" t="n">
         <v>0.055</v>
       </c>
-      <c r="H8" s="32" t="n">
+      <c r="H8" s="26" t="n">
         <v>-0.021</v>
       </c>
     </row>
-    <row r="9" ht="16" customHeight="1" s="29">
+    <row r="9" ht="16" customHeight="1" s="23">
       <c r="A9" s="2" t="inlineStr">
         <is>
           <t>2025-08</t>
         </is>
       </c>
-      <c r="B9" s="27" t="n">
+      <c r="B9" s="21" t="n">
         <v>2988</v>
       </c>
-      <c r="C9" s="27" t="n">
+      <c r="C9" s="21" t="n">
         <v>0.064</v>
       </c>
-      <c r="D9" s="31" t="n">
+      <c r="D9" s="25" t="n">
         <v>3085</v>
       </c>
-      <c r="E9" s="30" t="n">
+      <c r="E9" s="24" t="n">
         <v>0.08699999999999999</v>
       </c>
-      <c r="F9" s="30" t="n">
+      <c r="F9" s="24" t="n">
         <v>0.158</v>
       </c>
-      <c r="G9" s="30" t="n">
+      <c r="G9" s="24" t="n">
         <v>0.07199999999999999</v>
       </c>
-      <c r="H9" s="30" t="n">
+      <c r="H9" s="24" t="n">
         <v>0.049</v>
       </c>
     </row>
-    <row r="10" ht="16" customHeight="1" s="29">
+    <row r="10" ht="16" customHeight="1" s="23">
       <c r="A10" s="8" t="inlineStr">
         <is>
           <t>2025-09</t>
         </is>
       </c>
-      <c r="B10" s="28" t="n">
+      <c r="B10" s="22" t="n">
         <v>2960</v>
       </c>
-      <c r="C10" s="28" t="n">
+      <c r="C10" s="22" t="n">
         <v>0.061</v>
       </c>
-      <c r="D10" s="33" t="n">
+      <c r="D10" s="27" t="n">
         <v>3030</v>
       </c>
-      <c r="E10" s="32" t="n">
+      <c r="E10" s="26" t="n">
         <v>0.024</v>
       </c>
-      <c r="F10" s="32" t="n">
+      <c r="F10" s="26" t="n">
         <v>0.055</v>
       </c>
-      <c r="G10" s="32" t="n">
+      <c r="G10" s="26" t="n">
         <v>0.012</v>
       </c>
-      <c r="H10" s="32" t="n">
+      <c r="H10" s="26" t="n">
         <v>-0.051</v>
       </c>
     </row>
-    <row r="11" ht="16" customHeight="1" s="29">
+    <row r="11" ht="16" customHeight="1" s="23">
       <c r="A11" s="2" t="inlineStr">
         <is>
           <t>2025-10</t>
         </is>
       </c>
-      <c r="B11" s="27" t="n">
+      <c r="B11" s="21" t="n">
         <v>2925</v>
       </c>
-      <c r="C11" s="27" t="n">
+      <c r="C11" s="21" t="n">
         <v>0.06</v>
       </c>
-      <c r="D11" s="31" t="n">
+      <c r="D11" s="25" t="n">
         <v>3090</v>
       </c>
-      <c r="E11" s="30" t="n">
+      <c r="E11" s="24" t="n">
         <v>0.127</v>
       </c>
-      <c r="F11" s="30" t="n">
+      <c r="F11" s="24" t="n">
         <v>0.158</v>
       </c>
-      <c r="G11" s="30" t="n">
+      <c r="G11" s="24" t="n">
         <v>0.112</v>
       </c>
-      <c r="H11" s="30" t="n">
+      <c r="H11" s="24" t="n">
         <v>0.081</v>
       </c>
     </row>
-    <row r="12" ht="16" customHeight="1" s="29">
+    <row r="12" ht="16" customHeight="1" s="23">
       <c r="A12" s="8" t="inlineStr">
         <is>
           <t>2025-11</t>
         </is>
       </c>
-      <c r="B12" s="28" t="n">
+      <c r="B12" s="22" t="n">
         <v>2940</v>
       </c>
-      <c r="C12" s="28" t="n">
+      <c r="C12" s="22" t="n">
         <v>0.058</v>
       </c>
-      <c r="D12" s="33" t="n">
+      <c r="D12" s="27" t="n">
         <v>3120</v>
       </c>
-      <c r="E12" s="32" t="n">
+      <c r="E12" s="26" t="n">
         <v>0.067</v>
       </c>
-      <c r="F12" s="32" t="n">
+      <c r="F12" s="26" t="n">
         <v>0.095</v>
       </c>
-      <c r="G12" s="32" t="n">
+      <c r="G12" s="26" t="n">
         <v>0.048</v>
       </c>
-      <c r="H12" s="32" t="n">
+      <c r="H12" s="26" t="n">
         <v>0.022</v>
       </c>
     </row>
-    <row r="13" ht="16" customHeight="1" s="29">
+    <row r="13" ht="16" customHeight="1" s="23">
       <c r="A13" s="2" t="inlineStr">
         <is>
           <t>2025-12</t>
         </is>
       </c>
-      <c r="B13" s="27" t="n">
+      <c r="B13" s="21" t="n">
         <v>2990</v>
       </c>
-      <c r="C13" s="27" t="n">
+      <c r="C13" s="21" t="n">
         <v>0.062</v>
       </c>
-      <c r="D13" s="31" t="n">
+      <c r="D13" s="25" t="n">
         <v>3200</v>
       </c>
-      <c r="E13" s="30" t="n">
+      <c r="E13" s="24" t="n">
         <v>0.055</v>
       </c>
-      <c r="F13" s="30" t="n">
+      <c r="F13" s="24" t="n">
         <v>0.08799999999999999</v>
       </c>
-      <c r="G13" s="30" t="n">
+      <c r="G13" s="24" t="n">
         <v>0.039</v>
       </c>
-      <c r="H13" s="30" t="n">
+      <c r="H13" s="24" t="n">
         <v>0.015</v>
       </c>
     </row>
-    <row r="14" ht="16" customHeight="1" s="29">
+    <row r="14" ht="16" customHeight="1" s="23">
       <c r="A14" s="2" t="inlineStr">
         <is>
           <t>2026-01</t>
         </is>
       </c>
-      <c r="B14" s="24" t="n">
+      <c r="B14" s="18" t="n">
         <v>2938.5</v>
       </c>
-      <c r="C14" s="24" t="n">
+      <c r="C14" s="18" t="n">
         <v>0.098</v>
       </c>
-      <c r="D14" s="31" t="n">
+      <c r="D14" s="25" t="n">
         <v>3282.9</v>
       </c>
-      <c r="E14" s="30" t="n">
+      <c r="E14" s="24" t="n">
         <v>0.218</v>
       </c>
-      <c r="F14" s="30" t="n">
+      <c r="F14" s="24" t="n">
         <v>0.229</v>
       </c>
-      <c r="G14" s="30" t="n">
+      <c r="G14" s="24" t="n">
         <v>0.185</v>
       </c>
-      <c r="H14" s="30" t="n">
+      <c r="H14" s="24" t="n">
         <v>0.097</v>
       </c>
     </row>
-    <row r="15" ht="16" customHeight="1" s="29">
+    <row r="15" ht="16" customHeight="1" s="23">
       <c r="A15" s="2" t="inlineStr">
         <is>
           <t>2026-02</t>
         </is>
       </c>
-      <c r="B15" s="28" t="n">
+      <c r="B15" s="22" t="n">
         <v>2938.5</v>
       </c>
-      <c r="C15" s="28" t="n">
+      <c r="C15" s="22" t="n">
         <v>0.098</v>
       </c>
-      <c r="D15" s="33" t="n">
+      <c r="D15" s="27" t="n">
         <v>3282.9</v>
       </c>
-      <c r="E15" s="30" t="n">
+      <c r="E15" s="24" t="n">
         <v>0.218</v>
       </c>
-      <c r="F15" s="30" t="n">
+      <c r="F15" s="24" t="n">
         <v>0.229</v>
       </c>
-      <c r="G15" s="30" t="n">
+      <c r="G15" s="24" t="n">
         <v>0.185</v>
       </c>
-      <c r="H15" s="30" t="n">
+      <c r="H15" s="24" t="n">
         <v>0.097</v>
       </c>
     </row>
-    <row r="16" ht="16" customHeight="1" s="29">
+    <row r="16" ht="16" customHeight="1" s="23">
       <c r="A16" s="2" t="inlineStr">
         <is>
           <t>2026-03</t>
         </is>
       </c>
-      <c r="B16" s="27" t="n">
+      <c r="B16" s="21" t="n">
         <v>3087</v>
       </c>
-      <c r="C16" s="27" t="n">
+      <c r="C16" s="21" t="n">
         <v>0.047</v>
       </c>
-      <c r="D16" s="31" t="n">
+      <c r="D16" s="25" t="n">
         <v>3180</v>
       </c>
-      <c r="E16" s="30" t="n">
+      <c r="E16" s="24" t="n">
         <v>0.125</v>
       </c>
-      <c r="F16" s="30" t="n">
+      <c r="F16" s="24" t="n">
         <v>0.142</v>
       </c>
-      <c r="G16" s="30" t="n">
+      <c r="G16" s="24" t="n">
         <v>0.098</v>
       </c>
-      <c r="H16" s="30" t="n">
+      <c r="H16" s="24" t="n">
         <v>0.051</v>
       </c>
     </row>
-    <row r="17" ht="16" customHeight="1" s="29">
+    <row r="17" ht="16" customHeight="1" s="23">
       <c r="A17" s="2" t="inlineStr">
         <is>
           <t>2026-04</t>
         </is>
       </c>
-      <c r="B17" s="28" t="n">
+      <c r="B17" s="22" t="n">
         <v>3071</v>
       </c>
-      <c r="C17" s="28" t="n">
+      <c r="C17" s="22" t="n">
         <v>0.051</v>
       </c>
-      <c r="D17" s="33" t="n">
+      <c r="D17" s="27" t="n">
         <v>3210</v>
       </c>
-      <c r="E17" s="30" t="n">
+      <c r="E17" s="24" t="n">
         <v>0.108</v>
       </c>
-      <c r="F17" s="30" t="n">
+      <c r="F17" s="24" t="n">
         <v>0.135</v>
       </c>
-      <c r="G17" s="30" t="n">
+      <c r="G17" s="24" t="n">
         <v>0.082</v>
       </c>
-      <c r="H17" s="30" t="n">
+      <c r="H17" s="24" t="n">
         <v>0.038</v>
       </c>
     </row>
-    <row r="18" ht="16" customHeight="1" s="29">
+    <row r="18" ht="16" customHeight="1" s="23">
       <c r="A18" s="2" t="inlineStr">
         <is>
           <t>2026-05</t>
         </is>
       </c>
-      <c r="B18" s="27" t="n">
+      <c r="B18" s="21" t="n">
         <v>3130</v>
       </c>
-      <c r="C18" s="27" t="n">
+      <c r="C18" s="21" t="n">
         <v>0.031</v>
       </c>
-      <c r="D18" s="31" t="n">
+      <c r="D18" s="25" t="n">
         <v>3280</v>
       </c>
-      <c r="E18" s="30" t="n">
+      <c r="E18" s="24" t="n">
         <v>0.153</v>
       </c>
-      <c r="F18" s="30" t="n">
+      <c r="F18" s="24" t="n">
         <v>0.182</v>
       </c>
-      <c r="G18" s="30" t="n">
+      <c r="G18" s="24" t="n">
         <v>0.115</v>
       </c>
-      <c r="H18" s="30" t="n">
+      <c r="H18" s="24" t="n">
         <v>0.062</v>
       </c>
     </row>
-    <row r="19" ht="16" customHeight="1" s="29">
+    <row r="19" ht="16" customHeight="1" s="23">
       <c r="A19" s="2" t="inlineStr">
         <is>
           <t>2026-06</t>
         </is>
       </c>
-      <c r="B19" s="28" t="n">
+      <c r="B19" s="22" t="n">
         <v>3127</v>
       </c>
-      <c r="C19" s="28" t="n">
+      <c r="C19" s="22" t="n">
         <v>0.03</v>
       </c>
-      <c r="D19" s="33" t="n">
+      <c r="D19" s="27" t="n">
         <v>3320</v>
       </c>
-      <c r="E19" s="30" t="n">
+      <c r="E19" s="24" t="n">
         <v>0.102</v>
       </c>
-      <c r="F19" s="30" t="n">
+      <c r="F19" s="24" t="n">
         <v>0.128</v>
       </c>
-      <c r="G19" s="30" t="n">
+      <c r="G19" s="24" t="n">
         <v>0.079</v>
       </c>
-      <c r="H19" s="30" t="n">
+      <c r="H19" s="24" t="n">
         <v>0.025</v>
       </c>
     </row>
-    <row r="20" ht="16" customHeight="1" s="29">
+    <row r="20" ht="16" customHeight="1" s="23">
       <c r="A20" s="2" t="inlineStr">
         <is>
           <t>2026-07</t>
         </is>
       </c>
-      <c r="B20" s="27" t="n">
+      <c r="B20" s="21" t="n">
         <v>2990</v>
       </c>
-      <c r="C20" s="27" t="n">
+      <c r="C20" s="21" t="n">
         <v>-0.002</v>
       </c>
-      <c r="D20" s="31" t="n">
+      <c r="D20" s="25" t="n">
         <v>3290</v>
       </c>
-      <c r="E20" s="30" t="n">
+      <c r="E20" s="24" t="n">
         <v>0.08500000000000001</v>
       </c>
-      <c r="F20" s="30" t="n">
+      <c r="F20" s="24" t="n">
         <v>0.11</v>
       </c>
-      <c r="G20" s="30" t="n">
+      <c r="G20" s="24" t="n">
         <v>0.065</v>
       </c>
-      <c r="H20" s="30" t="n">
+      <c r="H20" s="24" t="n">
         <v>0.018</v>
       </c>
     </row>
-    <row r="21" ht="16" customHeight="1" s="29">
+    <row r="21" ht="16" customHeight="1" s="23">
       <c r="A21" s="2" t="inlineStr">
         <is>
           <t>2026-08</t>
         </is>
       </c>
-      <c r="B21" s="27" t="n"/>
-      <c r="C21" s="27" t="n"/>
-      <c r="D21" s="31" t="n">
+      <c r="B21" s="21" t="n">
+        <v>3012</v>
+      </c>
+      <c r="C21" s="21" t="n">
+        <v>-0.034</v>
+      </c>
+      <c r="D21" s="25" t="n">
         <v>4014.4</v>
       </c>
-      <c r="E21" s="30" t="n">
+      <c r="E21" s="24" t="n">
         <v>0.25</v>
       </c>
-      <c r="F21" s="30" t="n">
+      <c r="F21" s="24" t="n">
         <v>0.302</v>
       </c>
-      <c r="G21" s="30" t="n">
+      <c r="G21" s="24" t="n">
         <v>0.066</v>
       </c>
-      <c r="H21" s="30" t="n">
+      <c r="H21" s="24" t="n">
         <v>0.344</v>
       </c>
     </row>
@@ -2989,16 +2947,16 @@
   <dimension ref="A1:G8"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
-    <col width="20" customWidth="1" style="23" min="1" max="1"/>
-    <col width="30" customWidth="1" style="23" min="2" max="2"/>
-    <col width="18" customWidth="1" style="23" min="3" max="3"/>
-    <col width="24" customWidth="1" style="23" min="4" max="4"/>
-    <col width="22" customWidth="1" style="23" min="5" max="5"/>
-    <col width="18" customWidth="1" style="23" min="6" max="6"/>
-    <col width="68" customWidth="1" style="23" min="7" max="7"/>
+    <col width="20" customWidth="1" style="17" min="1" max="1"/>
+    <col width="30" customWidth="1" style="17" min="2" max="2"/>
+    <col width="18" customWidth="1" style="17" min="3" max="3"/>
+    <col width="24" customWidth="1" style="17" min="4" max="4"/>
+    <col width="22" customWidth="1" style="17" min="5" max="5"/>
+    <col width="18" customWidth="1" style="17" min="6" max="6"/>
+    <col width="68" customWidth="1" style="17" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row r="1" ht="18" customHeight="1" s="29">
+    <row r="1" ht="18" customHeight="1" s="23">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>时间节点</t>
@@ -3035,7 +2993,7 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="16" customHeight="1" s="29">
+    <row r="2" ht="16" customHeight="1" s="23">
       <c r="A2" s="2" t="inlineStr">
         <is>
           <t>2025 Q1</t>
@@ -3044,16 +3002,16 @@
       <c r="B2" s="7" t="n">
         <v>2980</v>
       </c>
-      <c r="C2" s="30" t="n">
+      <c r="C2" s="24" t="n">
         <v>0.082</v>
       </c>
-      <c r="D2" s="30" t="n">
+      <c r="D2" s="24" t="n">
         <v>0.245</v>
       </c>
-      <c r="E2" s="27" t="n">
+      <c r="E2" s="21" t="n">
         <v>28.5</v>
       </c>
-      <c r="F2" s="30" t="n">
+      <c r="F2" s="24" t="n">
         <v>0.0095</v>
       </c>
       <c r="G2" s="7" t="inlineStr">
@@ -3062,7 +3020,7 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="16" customHeight="1" s="29">
+    <row r="3" ht="16" customHeight="1" s="23">
       <c r="A3" s="8" t="inlineStr">
         <is>
           <t>2025 Q2</t>
@@ -3071,16 +3029,16 @@
       <c r="B3" s="13" t="n">
         <v>3030</v>
       </c>
-      <c r="C3" s="32" t="n">
+      <c r="C3" s="26" t="n">
         <v>0.079</v>
       </c>
-      <c r="D3" s="32" t="n">
+      <c r="D3" s="26" t="n">
         <v>0.228</v>
       </c>
-      <c r="E3" s="28" t="n">
+      <c r="E3" s="22" t="n">
         <v>24.2</v>
       </c>
-      <c r="F3" s="32" t="n">
+      <c r="F3" s="26" t="n">
         <v>0.008</v>
       </c>
       <c r="G3" s="13" t="inlineStr">
@@ -3089,7 +3047,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="16" customHeight="1" s="29">
+    <row r="4" ht="16" customHeight="1" s="23">
       <c r="A4" s="2" t="inlineStr">
         <is>
           <t>2025 Q3</t>
@@ -3098,16 +3056,16 @@
       <c r="B4" s="7" t="n">
         <v>3090</v>
       </c>
-      <c r="C4" s="30" t="n">
+      <c r="C4" s="24" t="n">
         <v>0.075</v>
       </c>
-      <c r="D4" s="30" t="n">
+      <c r="D4" s="24" t="n">
         <v>0.215</v>
       </c>
-      <c r="E4" s="27" t="n">
+      <c r="E4" s="21" t="n">
         <v>31</v>
       </c>
-      <c r="F4" s="30" t="n">
+      <c r="F4" s="24" t="n">
         <v>0.01</v>
       </c>
       <c r="G4" s="7" t="inlineStr">
@@ -3116,7 +3074,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="16" customHeight="1" s="29">
+    <row r="5" ht="16" customHeight="1" s="23">
       <c r="A5" s="8" t="inlineStr">
         <is>
           <t>2025 Q4</t>
@@ -3125,16 +3083,16 @@
       <c r="B5" s="13" t="n">
         <v>3140</v>
       </c>
-      <c r="C5" s="32" t="n">
+      <c r="C5" s="26" t="n">
         <v>0.07099999999999999</v>
       </c>
-      <c r="D5" s="32" t="n">
+      <c r="D5" s="26" t="n">
         <v>0.202</v>
       </c>
-      <c r="E5" s="28" t="n">
+      <c r="E5" s="22" t="n">
         <v>45</v>
       </c>
-      <c r="F5" s="32" t="n">
+      <c r="F5" s="26" t="n">
         <v>0.0143</v>
       </c>
       <c r="G5" s="13" t="inlineStr">
@@ -3143,7 +3101,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="16" customHeight="1" s="29">
+    <row r="6" ht="16" customHeight="1" s="23">
       <c r="A6" s="2" t="inlineStr">
         <is>
           <t>2026 Q1</t>
@@ -3152,16 +3110,16 @@
       <c r="B6" s="7" t="n">
         <v>3210</v>
       </c>
-      <c r="C6" s="30" t="n">
+      <c r="C6" s="24" t="n">
         <v>0.077</v>
       </c>
-      <c r="D6" s="30" t="n">
+      <c r="D6" s="24" t="n">
         <v>0.198</v>
       </c>
-      <c r="E6" s="27" t="n">
+      <c r="E6" s="21" t="n">
         <v>38</v>
       </c>
-      <c r="F6" s="30" t="n">
+      <c r="F6" s="24" t="n">
         <v>0.0118</v>
       </c>
       <c r="G6" s="7" t="inlineStr">
@@ -3170,7 +3128,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="16" customHeight="1" s="29">
+    <row r="7" ht="16" customHeight="1" s="23">
       <c r="A7" s="8" t="inlineStr">
         <is>
           <t>2026 Q2</t>
@@ -3179,16 +3137,16 @@
       <c r="B7" s="13" t="n">
         <v>3280</v>
       </c>
-      <c r="C7" s="32" t="n">
+      <c r="C7" s="26" t="n">
         <v>0.082</v>
       </c>
-      <c r="D7" s="32" t="n">
+      <c r="D7" s="26" t="n">
         <v>0.192</v>
       </c>
-      <c r="E7" s="28" t="n">
+      <c r="E7" s="22" t="n">
         <v>26</v>
       </c>
-      <c r="F7" s="32" t="n">
+      <c r="F7" s="26" t="n">
         <v>0.007900000000000001</v>
       </c>
       <c r="G7" s="13" t="inlineStr">
@@ -3197,7 +3155,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="16" customHeight="1" s="29">
+    <row r="8" ht="16" customHeight="1" s="23">
       <c r="A8" s="2" t="inlineStr">
         <is>
           <t>2026 Q3 (截至7月)</t>
@@ -3206,16 +3164,16 @@
       <c r="B8" s="7" t="n">
         <v>3320</v>
       </c>
-      <c r="C8" s="30" t="n">
+      <c r="C8" s="24" t="n">
         <v>0.074</v>
       </c>
-      <c r="D8" s="30" t="n">
+      <c r="D8" s="24" t="n">
         <v>0.188</v>
       </c>
-      <c r="E8" s="27" t="n">
+      <c r="E8" s="21" t="n">
         <v>29.8</v>
       </c>
-      <c r="F8" s="30" t="n">
+      <c r="F8" s="24" t="n">
         <v>0.008999999999999999</v>
       </c>
       <c r="G8" s="7" t="inlineStr">
@@ -3238,12 +3196,12 @@
   <dimension ref="A1:D8"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
-    <col width="20" customWidth="1" style="23" min="1" max="1"/>
-    <col width="26" customWidth="1" style="23" min="2" max="3"/>
-    <col width="85" customWidth="1" style="23" min="4" max="4"/>
+    <col width="20" customWidth="1" style="17" min="1" max="1"/>
+    <col width="26" customWidth="1" style="17" min="2" max="3"/>
+    <col width="85" customWidth="1" style="17" min="4" max="4"/>
   </cols>
   <sheetData>
-    <row r="1" ht="18" customHeight="1" s="29">
+    <row r="1" ht="18" customHeight="1" s="23">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>时间节点</t>
@@ -3265,16 +3223,16 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="16" customHeight="1" s="29">
+    <row r="2" ht="16" customHeight="1" s="23">
       <c r="A2" s="2" t="inlineStr">
         <is>
           <t>2025 Q1</t>
         </is>
       </c>
-      <c r="B2" s="30" t="n">
+      <c r="B2" s="24" t="n">
         <v>0.08500000000000001</v>
       </c>
-      <c r="C2" s="30" t="n">
+      <c r="C2" s="24" t="n">
         <v>0.062</v>
       </c>
       <c r="D2" s="7" t="inlineStr">
@@ -3283,16 +3241,16 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="16" customHeight="1" s="29">
+    <row r="3" ht="16" customHeight="1" s="23">
       <c r="A3" s="8" t="inlineStr">
         <is>
           <t>2025 Q2</t>
         </is>
       </c>
-      <c r="B3" s="32" t="n">
+      <c r="B3" s="26" t="n">
         <v>0.052</v>
       </c>
-      <c r="C3" s="32" t="n">
+      <c r="C3" s="26" t="n">
         <v>0.041</v>
       </c>
       <c r="D3" s="13" t="inlineStr">
@@ -3301,16 +3259,16 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="16" customHeight="1" s="29">
+    <row r="4" ht="16" customHeight="1" s="23">
       <c r="A4" s="2" t="inlineStr">
         <is>
           <t>2025 Q3</t>
         </is>
       </c>
-      <c r="B4" s="30" t="n">
+      <c r="B4" s="24" t="n">
         <v>0.078</v>
       </c>
-      <c r="C4" s="30" t="n">
+      <c r="C4" s="24" t="n">
         <v>0.055</v>
       </c>
       <c r="D4" s="7" t="inlineStr">
@@ -3319,16 +3277,16 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="16" customHeight="1" s="29">
+    <row r="5" ht="16" customHeight="1" s="23">
       <c r="A5" s="8" t="inlineStr">
         <is>
           <t>2025 Q4</t>
         </is>
       </c>
-      <c r="B5" s="32" t="n">
+      <c r="B5" s="26" t="n">
         <v>0.145</v>
       </c>
-      <c r="C5" s="32" t="n">
+      <c r="C5" s="26" t="n">
         <v>0.112</v>
       </c>
       <c r="D5" s="13" t="inlineStr">
@@ -3337,16 +3295,16 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="16" customHeight="1" s="29">
+    <row r="6" ht="16" customHeight="1" s="23">
       <c r="A6" s="2" t="inlineStr">
         <is>
           <t>2026 Q1</t>
         </is>
       </c>
-      <c r="B6" s="30" t="n">
+      <c r="B6" s="24" t="n">
         <v>0.122</v>
       </c>
-      <c r="C6" s="30" t="n">
+      <c r="C6" s="24" t="n">
         <v>0.098</v>
       </c>
       <c r="D6" s="7" t="inlineStr">
@@ -3355,16 +3313,16 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="16" customHeight="1" s="29">
+    <row r="7" ht="16" customHeight="1" s="23">
       <c r="A7" s="8" t="inlineStr">
         <is>
           <t>2026 Q2</t>
         </is>
       </c>
-      <c r="B7" s="32" t="n">
+      <c r="B7" s="26" t="n">
         <v>0.061</v>
       </c>
-      <c r="C7" s="32" t="n">
+      <c r="C7" s="26" t="n">
         <v>0.048</v>
       </c>
       <c r="D7" s="13" t="inlineStr">
@@ -3373,16 +3331,16 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="16" customHeight="1" s="29">
+    <row r="8" ht="16" customHeight="1" s="23">
       <c r="A8" s="2" t="inlineStr">
         <is>
           <t>2026 Q3 (截至7月)</t>
         </is>
       </c>
-      <c r="B8" s="30" t="n">
+      <c r="B8" s="24" t="n">
         <v>0.068</v>
       </c>
-      <c r="C8" s="30" t="n">
+      <c r="C8" s="24" t="n">
         <v>0.052</v>
       </c>
       <c r="D8" s="7" t="inlineStr">
